--- a/employees.xlsx
+++ b/employees.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{706AEEFC-B9D5-4817-A28E-5EF29B818CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661AD116-E102-4A7B-BAD0-2198FE560E3C}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{706AEEFC-B9D5-4817-A28E-5EF29B818CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E612350-16D6-4BAE-8079-6C5A3F17C870}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8265" uniqueCount="3542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8264" uniqueCount="3542">
   <si>
     <t>as_of_date=15 สิงหาคม 2569</t>
   </si>
@@ -10750,7 +10750,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10779,6 +10779,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -10810,7 +10816,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10888,6 +10894,9 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11015,6 +11024,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21386,9 +21399,7 @@
         <v>1170</v>
       </c>
       <c r="P165" s="9"/>
-      <c r="Q165" s="13" t="s">
-        <v>34</v>
-      </c>
+      <c r="Q165" s="27"/>
       <c r="R165" s="9"/>
       <c r="S165" s="9"/>
       <c r="T165" s="9"/>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{85CD52BF-2C13-4EA1-A181-6633CD8D816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="14_{85CD52BF-2C13-4EA1-A181-6633CD8D816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0FAF5B4-E75B-45CD-96D0-AC047D64B9C2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Departments!$A$1:$F$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$AE$569</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8173" uniqueCount="3504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8172" uniqueCount="3504">
   <si>
     <t>emp_id</t>
   </si>
@@ -10513,9 +10513,6 @@
     <t>thassnee@oceanglass.com</t>
   </si>
   <si>
-    <t>ห</t>
-  </si>
-  <si>
     <t>169034.jpg</t>
   </si>
   <si>
@@ -10550,6 +10547,9 @@
   </si>
   <si>
     <t>169035.jpg</t>
+  </si>
+  <si>
+    <t>as_of_date=15 ตุลาคม 2569</t>
   </si>
 </sst>
 </file>
@@ -10559,7 +10559,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10570,14 +10570,6 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF888888"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -10631,6 +10623,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -10697,9 +10701,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10713,85 +10717,89 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11146,31 +11154,31 @@
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
-        <v>3491</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
+        <v>3503</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
     </row>
     <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -19616,7 +19624,7 @@
       <c r="A139" s="8">
         <v>146037</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B139" s="33" t="s">
         <v>990</v>
       </c>
       <c r="C139" s="9" t="s">
@@ -19679,7 +19687,7 @@
       <c r="A140" s="8">
         <v>139013</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="33" t="s">
         <v>999</v>
       </c>
       <c r="C140" s="9" t="s">
@@ -19744,7 +19752,7 @@
       <c r="A141" s="8">
         <v>145015</v>
       </c>
-      <c r="B141" s="9" t="s">
+      <c r="B141" s="33" t="s">
         <v>1008</v>
       </c>
       <c r="C141" s="9" t="s">
@@ -19811,7 +19819,7 @@
       <c r="A142" s="8">
         <v>161005</v>
       </c>
-      <c r="B142" s="9" t="s">
+      <c r="B142" s="33" t="s">
         <v>1015</v>
       </c>
       <c r="C142" s="9" t="s">
@@ -19876,7 +19884,7 @@
       <c r="A143" s="8">
         <v>163003</v>
       </c>
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="33" t="s">
         <v>1022</v>
       </c>
       <c r="C143" s="9" t="s">
@@ -19943,7 +19951,7 @@
       <c r="A144" s="8">
         <v>166024</v>
       </c>
-      <c r="B144" s="9" t="s">
+      <c r="B144" s="33" t="s">
         <v>1028</v>
       </c>
       <c r="C144" s="9" t="s">
@@ -20008,7 +20016,7 @@
       <c r="A145" s="8">
         <v>167001</v>
       </c>
-      <c r="B145" s="9" t="s">
+      <c r="B145" s="33" t="s">
         <v>1035</v>
       </c>
       <c r="C145" s="9" t="s">
@@ -20073,7 +20081,7 @@
       <c r="A146" s="8">
         <v>167012</v>
       </c>
-      <c r="B146" s="9" t="s">
+      <c r="B146" s="33" t="s">
         <v>1043</v>
       </c>
       <c r="C146" s="9" t="s">
@@ -20132,7 +20140,7 @@
       <c r="A147" s="8">
         <v>260001</v>
       </c>
-      <c r="B147" s="9" t="s">
+      <c r="B147" s="33" t="s">
         <v>1049</v>
       </c>
       <c r="C147" s="9" t="s">
@@ -20199,7 +20207,7 @@
       <c r="A148" s="8">
         <v>267001</v>
       </c>
-      <c r="B148" s="9" t="s">
+      <c r="B148" s="33" t="s">
         <v>1057</v>
       </c>
       <c r="C148" s="9" t="s">
@@ -20264,7 +20272,7 @@
       <c r="A149" s="8">
         <v>160001</v>
       </c>
-      <c r="B149" s="9" t="s">
+      <c r="B149" s="33" t="s">
         <v>1064</v>
       </c>
       <c r="C149" s="9" t="s">
@@ -20622,9 +20630,7 @@
         <v>1103</v>
       </c>
       <c r="P154" s="9"/>
-      <c r="Q154" s="13" t="s">
-        <v>32</v>
-      </c>
+      <c r="Q154" s="9"/>
       <c r="R154" s="9"/>
       <c r="S154" s="9" t="s">
         <v>67</v>
@@ -20711,7 +20717,7 @@
       <c r="A156" s="8">
         <v>167020</v>
       </c>
-      <c r="B156" s="9" t="s">
+      <c r="B156" s="33" t="s">
         <v>1112</v>
       </c>
       <c r="C156" s="9" t="s">
@@ -20774,7 +20780,7 @@
       <c r="A157" s="8">
         <v>167029</v>
       </c>
-      <c r="B157" s="9" t="s">
+      <c r="B157" s="33" t="s">
         <v>1119</v>
       </c>
       <c r="C157" s="9" t="s">
@@ -20837,7 +20843,7 @@
       <c r="A158" s="8">
         <v>167032</v>
       </c>
-      <c r="B158" s="9" t="s">
+      <c r="B158" s="33" t="s">
         <v>1126</v>
       </c>
       <c r="C158" s="9" t="s">
@@ -20900,7 +20906,7 @@
       <c r="A159" s="8">
         <v>168024</v>
       </c>
-      <c r="B159" s="9" t="s">
+      <c r="B159" s="33" t="s">
         <v>1133</v>
       </c>
       <c r="C159" s="9" t="s">
@@ -21085,7 +21091,7 @@
       <c r="A162" s="8">
         <v>337004</v>
       </c>
-      <c r="B162" s="9" t="s">
+      <c r="B162" s="33" t="s">
         <v>1153</v>
       </c>
       <c r="C162" s="9" t="s">
@@ -21211,7 +21217,7 @@
       <c r="A164" s="8">
         <v>268044</v>
       </c>
-      <c r="B164" s="9" t="s">
+      <c r="B164" s="33" t="s">
         <v>1171</v>
       </c>
       <c r="C164" s="9" t="s">
@@ -21274,7 +21280,7 @@
       <c r="A165" s="8">
         <v>368004</v>
       </c>
-      <c r="B165" s="9" t="s">
+      <c r="B165" s="33" t="s">
         <v>1176</v>
       </c>
       <c r="C165" s="9" t="s">
@@ -21337,7 +21343,7 @@
       <c r="A166" s="8">
         <v>269040</v>
       </c>
-      <c r="B166" s="9" t="s">
+      <c r="B166" s="33" t="s">
         <v>1182</v>
       </c>
       <c r="C166" s="9" t="s">
@@ -21400,7 +21406,7 @@
       <c r="A167" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="B167" s="9" t="s">
+      <c r="B167" s="33" t="s">
         <v>1190</v>
       </c>
       <c r="C167" s="9" t="s">
@@ -43336,7 +43342,7 @@
       <c r="A529" s="8">
         <v>169024</v>
       </c>
-      <c r="B529" s="9" t="s">
+      <c r="B529" s="33" t="s">
         <v>3147</v>
       </c>
       <c r="C529" s="9" t="s">
@@ -45088,7 +45094,7 @@
       <c r="L558" s="12"/>
       <c r="M558" s="12"/>
       <c r="N558" s="9" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="O558" s="9"/>
       <c r="P558" s="9"/>
@@ -45145,7 +45151,7 @@
       <c r="L559" s="12"/>
       <c r="M559" s="12"/>
       <c r="N559" s="9" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="O559" s="9"/>
       <c r="P559" s="9"/>
@@ -45202,7 +45208,7 @@
       <c r="L560" s="12"/>
       <c r="M560" s="12"/>
       <c r="N560" s="9" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="O560" s="9" t="s">
         <v>3472</v>
@@ -45261,7 +45267,7 @@
       <c r="L561" s="12"/>
       <c r="M561" s="12"/>
       <c r="N561" s="9" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="O561" s="9" t="s">
         <v>3473</v>
@@ -45320,7 +45326,7 @@
       <c r="L562" s="12"/>
       <c r="M562" s="12"/>
       <c r="N562" s="9" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="O562" s="9" t="s">
         <v>3474</v>
@@ -45379,7 +45385,7 @@
       <c r="L563" s="12"/>
       <c r="M563" s="12"/>
       <c r="N563" s="9" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="O563" s="9" t="s">
         <v>3475</v>
@@ -45438,7 +45444,7 @@
       <c r="L564" s="12"/>
       <c r="M564" s="12"/>
       <c r="N564" s="9" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="O564" s="9" t="s">
         <v>3476</v>
@@ -45497,7 +45503,7 @@
       <c r="L565" s="12"/>
       <c r="M565" s="12"/>
       <c r="N565" s="9" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="O565" s="9" t="s">
         <v>3477</v>
@@ -45556,7 +45562,7 @@
       <c r="L566" s="12"/>
       <c r="M566" s="12"/>
       <c r="N566" s="9" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="O566" s="9"/>
       <c r="P566" s="9"/>
@@ -45613,7 +45619,7 @@
       <c r="L567" s="12"/>
       <c r="M567" s="12"/>
       <c r="N567" s="9" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="O567" s="9"/>
       <c r="P567" s="9"/>
@@ -45670,7 +45676,7 @@
       <c r="L568" s="12"/>
       <c r="M568" s="12"/>
       <c r="N568" s="9" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="O568" s="9" t="s">
         <v>3478</v>
@@ -45729,7 +45735,7 @@
       <c r="L569" s="12"/>
       <c r="M569" s="12"/>
       <c r="N569" s="9" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="O569" s="9" t="s">
         <v>3479</v>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="14_{85CD52BF-2C13-4EA1-A181-6633CD8D816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0FAF5B4-E75B-45CD-96D0-AC047D64B9C2}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="14_{85CD52BF-2C13-4EA1-A181-6633CD8D816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C87DA4C-3F97-4F6E-BF31-E74E12704F64}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
     <sheet name="Departments" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Departments!$A$1:$F$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employees!$A$2:$AE$569</definedName>
@@ -10795,13 +10798,13 @@
     <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10937,6 +10940,386 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="คำอธิบาย"/>
+      <sheetName val="กรอกข้อมูล"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>OCEAN GLASS  |  Succession Planning — Risk Assessment</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>emp_id</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>168028</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>150026</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>147022</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>136049</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>161027</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>656001</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>656008</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>168017</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>266049</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>166027</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>466004</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>159029</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>264090</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>239006</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>246004</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>242032</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>149024</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>268029 A</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>232027</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>256029</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>236012</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>250042</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>233034</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>268013</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>249010</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>268012</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>238030</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>256014</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>443003</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>254057</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>237011</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>267096</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>249048</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>269022</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>253014</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>248031</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>251007</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>242012</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>257039</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>244023</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>241009</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>368001</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>148005</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>267071</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>268051</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>269032</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>250051</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>146037</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>139013</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>145015</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>161005</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>163003</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>166024</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>167001</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>167012</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>260001</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>267001</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>160001</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>167020</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>167029</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>167032</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>168024</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>337004</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>267085</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>268044</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>368004</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>269040</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70" t="str">
+            <v>149024 A</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>168016</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>258026</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11122,10 +11505,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y1000"/>
+  <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="11.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
@@ -11152,35 +11535,35 @@
     <col min="26" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
         <v>3503</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-    </row>
-    <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+    </row>
+    <row r="2" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -11257,7 +11640,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>168001</v>
       </c>
@@ -11317,7 +11700,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>168016</v>
       </c>
@@ -11379,8 +11762,12 @@
         <v>33</v>
       </c>
       <c r="Y4" s="9"/>
-    </row>
-    <row r="5" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z4" s="15">
+        <f>_xlfn.XLOOKUP(A4,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>168016</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>258026</v>
       </c>
@@ -11446,8 +11833,12 @@
         <v>57</v>
       </c>
       <c r="Y5" s="9"/>
-    </row>
-    <row r="6" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z5" s="15">
+        <f>_xlfn.XLOOKUP(A5,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>258026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16">
         <v>234064</v>
       </c>
@@ -11510,7 +11901,7 @@
       </c>
       <c r="Y6" s="9"/>
     </row>
-    <row r="7" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16">
         <v>254019</v>
       </c>
@@ -11571,7 +11962,7 @@
       </c>
       <c r="Y7" s="9"/>
     </row>
-    <row r="8" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16">
         <v>264004</v>
       </c>
@@ -11632,7 +12023,7 @@
       </c>
       <c r="Y8" s="9"/>
     </row>
-    <row r="9" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16">
         <v>264018</v>
       </c>
@@ -11691,7 +12082,7 @@
       </c>
       <c r="Y9" s="9"/>
     </row>
-    <row r="10" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16">
         <v>264024</v>
       </c>
@@ -11752,7 +12143,7 @@
       </c>
       <c r="Y10" s="9"/>
     </row>
-    <row r="11" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16">
         <v>264034</v>
       </c>
@@ -11811,7 +12202,7 @@
       </c>
       <c r="Y11" s="9"/>
     </row>
-    <row r="12" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16">
         <v>265038</v>
       </c>
@@ -11870,7 +12261,7 @@
       </c>
       <c r="Y12" s="9"/>
     </row>
-    <row r="13" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16">
         <v>265122</v>
       </c>
@@ -11931,7 +12322,7 @@
       </c>
       <c r="Y13" s="9"/>
     </row>
-    <row r="14" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="16">
         <v>266005</v>
       </c>
@@ -11996,7 +12387,7 @@
       </c>
       <c r="Y14" s="9"/>
     </row>
-    <row r="15" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="16">
         <v>267010</v>
       </c>
@@ -12057,7 +12448,7 @@
       </c>
       <c r="Y15" s="9"/>
     </row>
-    <row r="16" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>267071</v>
       </c>
@@ -12119,8 +12510,12 @@
         <v>33</v>
       </c>
       <c r="Y16" s="9"/>
-    </row>
-    <row r="17" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z16" s="15">
+        <f>_xlfn.XLOOKUP(A16,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>267071</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="16">
         <v>267082</v>
       </c>
@@ -12181,7 +12576,7 @@
       </c>
       <c r="Y17" s="9"/>
     </row>
-    <row r="18" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="16">
         <v>267089</v>
       </c>
@@ -12240,7 +12635,7 @@
       </c>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="16">
         <v>267090</v>
       </c>
@@ -12299,7 +12694,7 @@
       </c>
       <c r="Y19" s="9"/>
     </row>
-    <row r="20" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="16">
         <v>268010</v>
       </c>
@@ -12358,7 +12753,7 @@
       </c>
       <c r="Y20" s="9"/>
     </row>
-    <row r="21" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="16">
         <v>268011</v>
       </c>
@@ -12417,7 +12812,7 @@
       </c>
       <c r="Y21" s="9"/>
     </row>
-    <row r="22" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>268051</v>
       </c>
@@ -12479,8 +12874,12 @@
         <v>33</v>
       </c>
       <c r="Y22" s="9"/>
-    </row>
-    <row r="23" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z22" s="15">
+        <f>_xlfn.XLOOKUP(A22,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>268051</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="16">
         <v>268060</v>
       </c>
@@ -12541,7 +12940,7 @@
       </c>
       <c r="Y23" s="9"/>
     </row>
-    <row r="24" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="16">
         <v>268065</v>
       </c>
@@ -12600,7 +12999,7 @@
       </c>
       <c r="Y24" s="9"/>
     </row>
-    <row r="25" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="16">
         <v>268066</v>
       </c>
@@ -12659,7 +13058,7 @@
       </c>
       <c r="Y25" s="9"/>
     </row>
-    <row r="26" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="16">
         <v>268067</v>
       </c>
@@ -12718,7 +13117,7 @@
       </c>
       <c r="Y26" s="9"/>
     </row>
-    <row r="27" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="16">
         <v>268085</v>
       </c>
@@ -12777,7 +13176,7 @@
       </c>
       <c r="Y27" s="9"/>
     </row>
-    <row r="28" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="16">
         <v>269023</v>
       </c>
@@ -12838,7 +13237,7 @@
       </c>
       <c r="Y28" s="9"/>
     </row>
-    <row r="29" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16">
         <v>255012</v>
       </c>
@@ -12899,7 +13298,7 @@
       </c>
       <c r="Y29" s="9"/>
     </row>
-    <row r="30" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="16">
         <v>259025</v>
       </c>
@@ -12964,7 +13363,7 @@
       </c>
       <c r="Y30" s="9"/>
     </row>
-    <row r="31" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16">
         <v>235035</v>
       </c>
@@ -13027,7 +13426,7 @@
       </c>
       <c r="Y31" s="9"/>
     </row>
-    <row r="32" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16">
         <v>253020</v>
       </c>
@@ -13088,7 +13487,7 @@
       </c>
       <c r="Y32" s="9"/>
     </row>
-    <row r="33" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>269032</v>
       </c>
@@ -13150,8 +13549,12 @@
         <v>33</v>
       </c>
       <c r="Y33" s="9"/>
-    </row>
-    <row r="34" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z33" s="15">
+        <f>_xlfn.XLOOKUP(A33,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>269032</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>250051</v>
       </c>
@@ -13217,8 +13620,12 @@
         <v>57</v>
       </c>
       <c r="Y34" s="9"/>
-    </row>
-    <row r="35" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z34" s="15">
+        <f>_xlfn.XLOOKUP(A34,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>250051</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="16">
         <v>254009</v>
       </c>
@@ -13277,7 +13684,7 @@
       </c>
       <c r="Y35" s="9"/>
     </row>
-    <row r="36" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="16">
         <v>254054</v>
       </c>
@@ -13336,7 +13743,7 @@
       </c>
       <c r="Y36" s="9"/>
     </row>
-    <row r="37" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="16">
         <v>255001</v>
       </c>
@@ -13395,7 +13802,7 @@
       </c>
       <c r="Y37" s="9"/>
     </row>
-    <row r="38" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="16">
         <v>255023</v>
       </c>
@@ -13458,7 +13865,7 @@
       </c>
       <c r="Y38" s="9"/>
     </row>
-    <row r="39" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16">
         <v>257010</v>
       </c>
@@ -13521,7 +13928,7 @@
       </c>
       <c r="Y39" s="9"/>
     </row>
-    <row r="40" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16">
         <v>257029</v>
       </c>
@@ -13582,7 +13989,7 @@
       </c>
       <c r="Y40" s="9"/>
     </row>
-    <row r="41" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="16">
         <v>261023</v>
       </c>
@@ -13643,7 +14050,7 @@
       </c>
       <c r="Y41" s="9"/>
     </row>
-    <row r="42" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="16">
         <v>267025</v>
       </c>
@@ -13702,7 +14109,7 @@
       </c>
       <c r="Y42" s="9"/>
     </row>
-    <row r="43" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="16">
         <v>267026</v>
       </c>
@@ -13761,7 +14168,7 @@
       </c>
       <c r="Y43" s="9"/>
     </row>
-    <row r="44" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="16">
         <v>267028</v>
       </c>
@@ -13822,7 +14229,7 @@
       </c>
       <c r="Y44" s="9"/>
     </row>
-    <row r="45" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="16">
         <v>267079</v>
       </c>
@@ -13881,7 +14288,7 @@
       </c>
       <c r="Y45" s="9"/>
     </row>
-    <row r="46" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="16">
         <v>267100</v>
       </c>
@@ -13936,7 +14343,7 @@
       </c>
       <c r="Y46" s="9"/>
     </row>
-    <row r="47" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="16">
         <v>267101</v>
       </c>
@@ -13991,7 +14398,7 @@
       </c>
       <c r="Y47" s="9"/>
     </row>
-    <row r="48" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="16">
         <v>267105</v>
       </c>
@@ -14046,7 +14453,7 @@
       </c>
       <c r="Y48" s="9"/>
     </row>
-    <row r="49" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="16">
         <v>268016</v>
       </c>
@@ -14107,7 +14514,7 @@
       </c>
       <c r="Y49" s="9"/>
     </row>
-    <row r="50" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="16">
         <v>268059</v>
       </c>
@@ -14168,7 +14575,7 @@
       </c>
       <c r="Y50" s="9"/>
     </row>
-    <row r="51" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="16">
         <v>268061</v>
       </c>
@@ -14227,7 +14634,7 @@
       </c>
       <c r="Y51" s="9"/>
     </row>
-    <row r="52" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="16">
         <v>268079</v>
       </c>
@@ -14286,7 +14693,7 @@
       </c>
       <c r="Y52" s="9"/>
     </row>
-    <row r="53" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="16">
         <v>268082</v>
       </c>
@@ -14345,7 +14752,7 @@
       </c>
       <c r="Y53" s="9"/>
     </row>
-    <row r="54" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="16">
         <v>269027</v>
       </c>
@@ -14404,7 +14811,7 @@
       </c>
       <c r="Y54" s="9"/>
     </row>
-    <row r="55" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>159029</v>
       </c>
@@ -14470,8 +14877,12 @@
       <c r="Y55" s="9" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="56" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z55" s="15">
+        <f>_xlfn.XLOOKUP(A55,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>159029</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="16">
         <v>164005</v>
       </c>
@@ -14536,7 +14947,7 @@
       </c>
       <c r="Y56" s="9"/>
     </row>
-    <row r="57" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="16">
         <v>152008</v>
       </c>
@@ -14599,7 +15010,7 @@
       </c>
       <c r="Y57" s="9"/>
     </row>
-    <row r="58" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="16">
         <v>267063</v>
       </c>
@@ -14660,7 +15071,7 @@
       </c>
       <c r="Y58" s="9"/>
     </row>
-    <row r="59" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>168017</v>
       </c>
@@ -14722,8 +15133,12 @@
         <v>33</v>
       </c>
       <c r="Y59" s="9"/>
-    </row>
-    <row r="60" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z59" s="15">
+        <f>_xlfn.XLOOKUP(A59,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>168017</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="16">
         <v>167034</v>
       </c>
@@ -14784,7 +15199,7 @@
       </c>
       <c r="Y60" s="9"/>
     </row>
-    <row r="61" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="8">
         <v>266049</v>
       </c>
@@ -14850,8 +15265,12 @@
       <c r="Y61" s="9" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="62" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z61" s="15">
+        <f>_xlfn.XLOOKUP(A61,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>266049</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>466004</v>
       </c>
@@ -14913,8 +15332,12 @@
         <v>33</v>
       </c>
       <c r="Y62" s="9"/>
-    </row>
-    <row r="63" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z62" s="15">
+        <f>_xlfn.XLOOKUP(A62,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>466004</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="16">
         <v>269013</v>
       </c>
@@ -14975,7 +15398,7 @@
       </c>
       <c r="Y63" s="9"/>
     </row>
-    <row r="64" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="16">
         <v>269001</v>
       </c>
@@ -15036,7 +15459,7 @@
       </c>
       <c r="Y64" s="9"/>
     </row>
-    <row r="65" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="16">
         <v>265088</v>
       </c>
@@ -15097,7 +15520,7 @@
       </c>
       <c r="Y65" s="9"/>
     </row>
-    <row r="66" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="16">
         <v>239005</v>
       </c>
@@ -15160,7 +15583,7 @@
       </c>
       <c r="Y66" s="9"/>
     </row>
-    <row r="67" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="8">
         <v>166027</v>
       </c>
@@ -15222,8 +15645,12 @@
         <v>57</v>
       </c>
       <c r="Y67" s="9"/>
-    </row>
-    <row r="68" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z67" s="15">
+        <f>_xlfn.XLOOKUP(A67,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>166027</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="16">
         <v>168018</v>
       </c>
@@ -15284,7 +15711,7 @@
       </c>
       <c r="Y68" s="9"/>
     </row>
-    <row r="69" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="16">
         <v>157033</v>
       </c>
@@ -15347,7 +15774,7 @@
       </c>
       <c r="Y69" s="9"/>
     </row>
-    <row r="70" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="16">
         <v>169001</v>
       </c>
@@ -15408,7 +15835,7 @@
       </c>
       <c r="Y70" s="9"/>
     </row>
-    <row r="71" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="16">
         <v>166035</v>
       </c>
@@ -15469,7 +15896,7 @@
       </c>
       <c r="Y71" s="9"/>
     </row>
-    <row r="72" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="16">
         <v>269014</v>
       </c>
@@ -15530,7 +15957,7 @@
       </c>
       <c r="Y72" s="9"/>
     </row>
-    <row r="73" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="16">
         <v>166032</v>
       </c>
@@ -15591,7 +16018,7 @@
       </c>
       <c r="Y73" s="9"/>
     </row>
-    <row r="74" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="16">
         <v>169017</v>
       </c>
@@ -15652,7 +16079,7 @@
       </c>
       <c r="Y74" s="9"/>
     </row>
-    <row r="75" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="16">
         <v>265011</v>
       </c>
@@ -15717,7 +16144,7 @@
       </c>
       <c r="Y75" s="9"/>
     </row>
-    <row r="76" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:26" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="8">
         <v>168015</v>
       </c>
@@ -15779,8 +16206,12 @@
       <c r="Y76" s="9" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="77" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z76" s="15" t="e">
+        <f>_xlfn.XLOOKUP(A76,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="16">
         <v>168004</v>
       </c>
@@ -15841,7 +16272,7 @@
       </c>
       <c r="Y77" s="9"/>
     </row>
-    <row r="78" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="8">
         <v>168028</v>
       </c>
@@ -15903,8 +16334,12 @@
         <v>33</v>
       </c>
       <c r="Y78" s="9"/>
-    </row>
-    <row r="79" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z78" s="15">
+        <f>_xlfn.XLOOKUP(A78,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>168028</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="16">
         <v>160023</v>
       </c>
@@ -15969,7 +16404,7 @@
       </c>
       <c r="Y79" s="9"/>
     </row>
-    <row r="80" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="8">
         <v>150026</v>
       </c>
@@ -16035,8 +16470,12 @@
         <v>57</v>
       </c>
       <c r="Y80" s="9"/>
-    </row>
-    <row r="81" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z80" s="15">
+        <f>_xlfn.XLOOKUP(A80,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>150026</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="16">
         <v>161016</v>
       </c>
@@ -16101,7 +16540,7 @@
       </c>
       <c r="Y81" s="9"/>
     </row>
-    <row r="82" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="16">
         <v>161006</v>
       </c>
@@ -16166,7 +16605,7 @@
       </c>
       <c r="Y82" s="9"/>
     </row>
-    <row r="83" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="16">
         <v>164014</v>
       </c>
@@ -16223,7 +16662,7 @@
       </c>
       <c r="Y83" s="9"/>
     </row>
-    <row r="84" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="16">
         <v>166009</v>
       </c>
@@ -16284,7 +16723,7 @@
       </c>
       <c r="Y84" s="9"/>
     </row>
-    <row r="85" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="16">
         <v>168038</v>
       </c>
@@ -16345,7 +16784,7 @@
       </c>
       <c r="Y85" s="9"/>
     </row>
-    <row r="86" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="16">
         <v>168041</v>
       </c>
@@ -16406,7 +16845,7 @@
       </c>
       <c r="Y86" s="9"/>
     </row>
-    <row r="87" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="16">
         <v>169021</v>
       </c>
@@ -16467,7 +16906,7 @@
       </c>
       <c r="Y87" s="9"/>
     </row>
-    <row r="88" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="16">
         <v>147016</v>
       </c>
@@ -16532,7 +16971,7 @@
       </c>
       <c r="Y88" s="9"/>
     </row>
-    <row r="89" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="16">
         <v>148017</v>
       </c>
@@ -16593,7 +17032,7 @@
       </c>
       <c r="Y89" s="9"/>
     </row>
-    <row r="90" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="16">
         <v>150010</v>
       </c>
@@ -16658,7 +17097,7 @@
       </c>
       <c r="Y90" s="9"/>
     </row>
-    <row r="91" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="16">
         <v>166021</v>
       </c>
@@ -16721,7 +17160,7 @@
       </c>
       <c r="Y91" s="9"/>
     </row>
-    <row r="92" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="16">
         <v>167004</v>
       </c>
@@ -16782,7 +17221,7 @@
       </c>
       <c r="Y92" s="9"/>
     </row>
-    <row r="93" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="16">
         <v>167023</v>
       </c>
@@ -16843,7 +17282,7 @@
       </c>
       <c r="Y93" s="9"/>
     </row>
-    <row r="94" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="16">
         <v>169003</v>
       </c>
@@ -16904,7 +17343,7 @@
       </c>
       <c r="Y94" s="9"/>
     </row>
-    <row r="95" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="8">
         <v>147022</v>
       </c>
@@ -16970,8 +17409,12 @@
         <v>57</v>
       </c>
       <c r="Y95" s="9"/>
-    </row>
-    <row r="96" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z95" s="15">
+        <f>_xlfn.XLOOKUP(A95,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>147022</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="16">
         <v>165014</v>
       </c>
@@ -17032,7 +17475,7 @@
       </c>
       <c r="Y96" s="9"/>
     </row>
-    <row r="97" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="16">
         <v>166028</v>
       </c>
@@ -17095,7 +17538,7 @@
       </c>
       <c r="Y97" s="9"/>
     </row>
-    <row r="98" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="16">
         <v>167015</v>
       </c>
@@ -17156,7 +17599,7 @@
       </c>
       <c r="Y98" s="9"/>
     </row>
-    <row r="99" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="16">
         <v>168014</v>
       </c>
@@ -17217,7 +17660,7 @@
       </c>
       <c r="Y99" s="9"/>
     </row>
-    <row r="100" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="16">
         <v>168022</v>
       </c>
@@ -17280,7 +17723,7 @@
       </c>
       <c r="Y100" s="9"/>
     </row>
-    <row r="101" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="16">
         <v>168037</v>
       </c>
@@ -17341,7 +17784,7 @@
       </c>
       <c r="Y101" s="9"/>
     </row>
-    <row r="102" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="16">
         <v>333003</v>
       </c>
@@ -17398,7 +17841,7 @@
       </c>
       <c r="Y102" s="9"/>
     </row>
-    <row r="103" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="16">
         <v>168010</v>
       </c>
@@ -17459,7 +17902,7 @@
       </c>
       <c r="Y103" s="9"/>
     </row>
-    <row r="104" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="8">
         <v>136049</v>
       </c>
@@ -17525,8 +17968,12 @@
         <v>57</v>
       </c>
       <c r="Y104" s="9"/>
-    </row>
-    <row r="105" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z104" s="15">
+        <f>_xlfn.XLOOKUP(A104,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>136049</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="16">
         <v>135071</v>
       </c>
@@ -17587,7 +18034,7 @@
       </c>
       <c r="Y105" s="9"/>
     </row>
-    <row r="106" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="16">
         <v>156025</v>
       </c>
@@ -17648,7 +18095,7 @@
       </c>
       <c r="Y106" s="9"/>
     </row>
-    <row r="107" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="16">
         <v>165027</v>
       </c>
@@ -17711,7 +18158,7 @@
       </c>
       <c r="Y107" s="9"/>
     </row>
-    <row r="108" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="16">
         <v>169005</v>
       </c>
@@ -17772,7 +18219,7 @@
       </c>
       <c r="Y108" s="9"/>
     </row>
-    <row r="109" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="16">
         <v>155015</v>
       </c>
@@ -17837,7 +18284,7 @@
       </c>
       <c r="Y109" s="9"/>
     </row>
-    <row r="110" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="16">
         <v>166025</v>
       </c>
@@ -17900,7 +18347,7 @@
       </c>
       <c r="Y110" s="9"/>
     </row>
-    <row r="111" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="16">
         <v>167027</v>
       </c>
@@ -17957,7 +18404,7 @@
       </c>
       <c r="Y111" s="9"/>
     </row>
-    <row r="112" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="16">
         <v>168019</v>
       </c>
@@ -18014,7 +18461,7 @@
       </c>
       <c r="Y112" s="9"/>
     </row>
-    <row r="113" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="16">
         <v>139011</v>
       </c>
@@ -18071,7 +18518,7 @@
       </c>
       <c r="Y113" s="9"/>
     </row>
-    <row r="114" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="16">
         <v>159042</v>
       </c>
@@ -18136,7 +18583,7 @@
       </c>
       <c r="Y114" s="9"/>
     </row>
-    <row r="115" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="16">
         <v>164024</v>
       </c>
@@ -18201,7 +18648,7 @@
       </c>
       <c r="Y115" s="9"/>
     </row>
-    <row r="116" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="16">
         <v>166002</v>
       </c>
@@ -18264,7 +18711,7 @@
       </c>
       <c r="Y116" s="9"/>
     </row>
-    <row r="117" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="16">
         <v>167005</v>
       </c>
@@ -18325,7 +18772,7 @@
       </c>
       <c r="Y117" s="9"/>
     </row>
-    <row r="118" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="16">
         <v>168021</v>
       </c>
@@ -18386,7 +18833,7 @@
       </c>
       <c r="Y118" s="9"/>
     </row>
-    <row r="119" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="16">
         <v>168033</v>
       </c>
@@ -18443,7 +18890,7 @@
       </c>
       <c r="Y119" s="9"/>
     </row>
-    <row r="120" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="16">
         <v>168036</v>
       </c>
@@ -18504,7 +18951,7 @@
       </c>
       <c r="Y120" s="9"/>
     </row>
-    <row r="121" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="16">
         <v>161001</v>
       </c>
@@ -18569,7 +19016,7 @@
       </c>
       <c r="Y121" s="9"/>
     </row>
-    <row r="122" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="16">
         <v>166020</v>
       </c>
@@ -18632,7 +19079,7 @@
       </c>
       <c r="Y122" s="9"/>
     </row>
-    <row r="123" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="16">
         <v>167017</v>
       </c>
@@ -18695,7 +19142,7 @@
       </c>
       <c r="Y123" s="9"/>
     </row>
-    <row r="124" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="16">
         <v>168020</v>
       </c>
@@ -18756,7 +19203,7 @@
       </c>
       <c r="Y124" s="9"/>
     </row>
-    <row r="125" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="16">
         <v>168025</v>
       </c>
@@ -18813,7 +19260,7 @@
       </c>
       <c r="Y125" s="9"/>
     </row>
-    <row r="126" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="16">
         <v>169010</v>
       </c>
@@ -18874,7 +19321,7 @@
       </c>
       <c r="Y126" s="9"/>
     </row>
-    <row r="127" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="16">
         <v>154012</v>
       </c>
@@ -18935,7 +19382,7 @@
       </c>
       <c r="Y127" s="9"/>
     </row>
-    <row r="128" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="16">
         <v>165005</v>
       </c>
@@ -18996,7 +19443,7 @@
       </c>
       <c r="Y128" s="9"/>
     </row>
-    <row r="129" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="16">
         <v>166019</v>
       </c>
@@ -19057,7 +19504,7 @@
       </c>
       <c r="Y129" s="9"/>
     </row>
-    <row r="130" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="16">
         <v>168005</v>
       </c>
@@ -19114,7 +19561,7 @@
       </c>
       <c r="Y130" s="9"/>
     </row>
-    <row r="131" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="16">
         <v>168023</v>
       </c>
@@ -19175,7 +19622,7 @@
       </c>
       <c r="Y131" s="9"/>
     </row>
-    <row r="132" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="16">
         <v>169004</v>
       </c>
@@ -19236,7 +19683,7 @@
       </c>
       <c r="Y132" s="9"/>
     </row>
-    <row r="133" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="16">
         <v>156026</v>
       </c>
@@ -19301,7 +19748,7 @@
       </c>
       <c r="Y133" s="9"/>
     </row>
-    <row r="134" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="16">
         <v>166014</v>
       </c>
@@ -19364,7 +19811,7 @@
       </c>
       <c r="Y134" s="9"/>
     </row>
-    <row r="135" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="16">
         <v>156031</v>
       </c>
@@ -19427,7 +19874,7 @@
       </c>
       <c r="Y135" s="9"/>
     </row>
-    <row r="136" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="8">
         <v>161027</v>
       </c>
@@ -19493,8 +19940,12 @@
         <v>57</v>
       </c>
       <c r="Y136" s="9"/>
-    </row>
-    <row r="137" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z136" s="15">
+        <f>_xlfn.XLOOKUP(A136,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>161027</v>
+      </c>
+    </row>
+    <row r="137" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="16">
         <v>164032</v>
       </c>
@@ -19559,7 +20010,7 @@
       </c>
       <c r="Y137" s="9"/>
     </row>
-    <row r="138" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="16">
         <v>168008</v>
       </c>
@@ -19620,11 +20071,11 @@
       </c>
       <c r="Y138" s="9"/>
     </row>
-    <row r="139" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="8">
         <v>146037</v>
       </c>
-      <c r="B139" s="33" t="s">
+      <c r="B139" s="31" t="s">
         <v>990</v>
       </c>
       <c r="C139" s="9" t="s">
@@ -19682,12 +20133,16 @@
         <v>57</v>
       </c>
       <c r="Y139" s="9"/>
-    </row>
-    <row r="140" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z139" s="15">
+        <f>_xlfn.XLOOKUP(A139,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>146037</v>
+      </c>
+    </row>
+    <row r="140" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="8">
         <v>139013</v>
       </c>
-      <c r="B140" s="33" t="s">
+      <c r="B140" s="31" t="s">
         <v>999</v>
       </c>
       <c r="C140" s="9" t="s">
@@ -19747,12 +20202,16 @@
         <v>57</v>
       </c>
       <c r="Y140" s="9"/>
-    </row>
-    <row r="141" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z140" s="15">
+        <f>_xlfn.XLOOKUP(A140,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>139013</v>
+      </c>
+    </row>
+    <row r="141" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="8">
         <v>145015</v>
       </c>
-      <c r="B141" s="33" t="s">
+      <c r="B141" s="31" t="s">
         <v>1008</v>
       </c>
       <c r="C141" s="9" t="s">
@@ -19814,12 +20273,16 @@
         <v>57</v>
       </c>
       <c r="Y141" s="9"/>
-    </row>
-    <row r="142" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z141" s="15">
+        <f>_xlfn.XLOOKUP(A141,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>145015</v>
+      </c>
+    </row>
+    <row r="142" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="8">
         <v>161005</v>
       </c>
-      <c r="B142" s="33" t="s">
+      <c r="B142" s="31" t="s">
         <v>1015</v>
       </c>
       <c r="C142" s="9" t="s">
@@ -19879,12 +20342,16 @@
         <v>57</v>
       </c>
       <c r="Y142" s="9"/>
-    </row>
-    <row r="143" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z142" s="15">
+        <f>_xlfn.XLOOKUP(A142,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>161005</v>
+      </c>
+    </row>
+    <row r="143" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="8">
         <v>163003</v>
       </c>
-      <c r="B143" s="33" t="s">
+      <c r="B143" s="31" t="s">
         <v>1022</v>
       </c>
       <c r="C143" s="9" t="s">
@@ -19946,12 +20413,16 @@
         <v>57</v>
       </c>
       <c r="Y143" s="9"/>
-    </row>
-    <row r="144" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z143" s="15">
+        <f>_xlfn.XLOOKUP(A143,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>163003</v>
+      </c>
+    </row>
+    <row r="144" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="8">
         <v>166024</v>
       </c>
-      <c r="B144" s="33" t="s">
+      <c r="B144" s="31" t="s">
         <v>1028</v>
       </c>
       <c r="C144" s="9" t="s">
@@ -20011,12 +20482,16 @@
         <v>57</v>
       </c>
       <c r="Y144" s="9"/>
-    </row>
-    <row r="145" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z144" s="15">
+        <f>_xlfn.XLOOKUP(A144,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>166024</v>
+      </c>
+    </row>
+    <row r="145" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="8">
         <v>167001</v>
       </c>
-      <c r="B145" s="33" t="s">
+      <c r="B145" s="31" t="s">
         <v>1035</v>
       </c>
       <c r="C145" s="9" t="s">
@@ -20076,12 +20551,16 @@
         <v>57</v>
       </c>
       <c r="Y145" s="9"/>
-    </row>
-    <row r="146" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z145" s="15">
+        <f>_xlfn.XLOOKUP(A145,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>167001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="8">
         <v>167012</v>
       </c>
-      <c r="B146" s="33" t="s">
+      <c r="B146" s="31" t="s">
         <v>1043</v>
       </c>
       <c r="C146" s="9" t="s">
@@ -20135,12 +20614,16 @@
         <v>33</v>
       </c>
       <c r="Y146" s="9"/>
-    </row>
-    <row r="147" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z146" s="15">
+        <f>_xlfn.XLOOKUP(A146,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>167012</v>
+      </c>
+    </row>
+    <row r="147" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="8">
         <v>260001</v>
       </c>
-      <c r="B147" s="33" t="s">
+      <c r="B147" s="31" t="s">
         <v>1049</v>
       </c>
       <c r="C147" s="9" t="s">
@@ -20202,12 +20685,16 @@
         <v>57</v>
       </c>
       <c r="Y147" s="9"/>
-    </row>
-    <row r="148" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z147" s="15">
+        <f>_xlfn.XLOOKUP(A147,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>260001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="8">
         <v>267001</v>
       </c>
-      <c r="B148" s="33" t="s">
+      <c r="B148" s="31" t="s">
         <v>1057</v>
       </c>
       <c r="C148" s="9" t="s">
@@ -20267,12 +20754,16 @@
         <v>57</v>
       </c>
       <c r="Y148" s="9"/>
-    </row>
-    <row r="149" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z148" s="15">
+        <f>_xlfn.XLOOKUP(A148,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>267001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="8">
         <v>160001</v>
       </c>
-      <c r="B149" s="33" t="s">
+      <c r="B149" s="31" t="s">
         <v>1064</v>
       </c>
       <c r="C149" s="9" t="s">
@@ -20334,8 +20825,12 @@
         <v>57</v>
       </c>
       <c r="Y149" s="9"/>
-    </row>
-    <row r="150" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z149" s="15">
+        <f>_xlfn.XLOOKUP(A149,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>160001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="16">
         <v>135095</v>
       </c>
@@ -20396,7 +20891,7 @@
       </c>
       <c r="Y150" s="9"/>
     </row>
-    <row r="151" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="16">
         <v>159019</v>
       </c>
@@ -20457,7 +20952,7 @@
       </c>
       <c r="Y151" s="9"/>
     </row>
-    <row r="152" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="16">
         <v>160013</v>
       </c>
@@ -20522,7 +21017,7 @@
       </c>
       <c r="Y152" s="9"/>
     </row>
-    <row r="153" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="16">
         <v>164008</v>
       </c>
@@ -20587,7 +21082,7 @@
       </c>
       <c r="Y153" s="9"/>
     </row>
-    <row r="154" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="8">
         <v>165004</v>
       </c>
@@ -20650,7 +21145,7 @@
       </c>
       <c r="Y154" s="9"/>
     </row>
-    <row r="155" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="16">
         <v>167013</v>
       </c>
@@ -20713,11 +21208,11 @@
       </c>
       <c r="Y155" s="9"/>
     </row>
-    <row r="156" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="8">
         <v>167020</v>
       </c>
-      <c r="B156" s="33" t="s">
+      <c r="B156" s="31" t="s">
         <v>1112</v>
       </c>
       <c r="C156" s="9" t="s">
@@ -20775,12 +21270,16 @@
         <v>33</v>
       </c>
       <c r="Y156" s="9"/>
-    </row>
-    <row r="157" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z156" s="15">
+        <f>_xlfn.XLOOKUP(A156,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>167020</v>
+      </c>
+    </row>
+    <row r="157" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="8">
         <v>167029</v>
       </c>
-      <c r="B157" s="33" t="s">
+      <c r="B157" s="31" t="s">
         <v>1119</v>
       </c>
       <c r="C157" s="9" t="s">
@@ -20838,12 +21337,16 @@
         <v>33</v>
       </c>
       <c r="Y157" s="9"/>
-    </row>
-    <row r="158" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z157" s="15">
+        <f>_xlfn.XLOOKUP(A157,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>167029</v>
+      </c>
+    </row>
+    <row r="158" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="8">
         <v>167032</v>
       </c>
-      <c r="B158" s="33" t="s">
+      <c r="B158" s="31" t="s">
         <v>1126</v>
       </c>
       <c r="C158" s="9" t="s">
@@ -20901,12 +21404,16 @@
         <v>33</v>
       </c>
       <c r="Y158" s="9"/>
-    </row>
-    <row r="159" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z158" s="15">
+        <f>_xlfn.XLOOKUP(A158,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>167032</v>
+      </c>
+    </row>
+    <row r="159" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="8">
         <v>168024</v>
       </c>
-      <c r="B159" s="33" t="s">
+      <c r="B159" s="31" t="s">
         <v>1133</v>
       </c>
       <c r="C159" s="9" t="s">
@@ -20964,8 +21471,12 @@
         <v>33</v>
       </c>
       <c r="Y159" s="9"/>
-    </row>
-    <row r="160" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z159" s="15">
+        <f>_xlfn.XLOOKUP(A159,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>168024</v>
+      </c>
+    </row>
+    <row r="160" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="8">
         <v>168029</v>
       </c>
@@ -21026,7 +21537,7 @@
       </c>
       <c r="Y160" s="9"/>
     </row>
-    <row r="161" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="16">
         <v>169006</v>
       </c>
@@ -21087,11 +21598,11 @@
       </c>
       <c r="Y161" s="9"/>
     </row>
-    <row r="162" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="8">
         <v>337004</v>
       </c>
-      <c r="B162" s="33" t="s">
+      <c r="B162" s="31" t="s">
         <v>1153</v>
       </c>
       <c r="C162" s="9" t="s">
@@ -21151,8 +21662,12 @@
         <v>57</v>
       </c>
       <c r="Y162" s="9"/>
-    </row>
-    <row r="163" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z162" s="15">
+        <f>_xlfn.XLOOKUP(A162,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>337004</v>
+      </c>
+    </row>
+    <row r="163" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="16">
         <v>364002</v>
       </c>
@@ -21213,11 +21728,11 @@
       </c>
       <c r="Y163" s="9"/>
     </row>
-    <row r="164" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="8">
         <v>268044</v>
       </c>
-      <c r="B164" s="33" t="s">
+      <c r="B164" s="31" t="s">
         <v>1171</v>
       </c>
       <c r="C164" s="9" t="s">
@@ -21275,12 +21790,16 @@
         <v>33</v>
       </c>
       <c r="Y164" s="9"/>
-    </row>
-    <row r="165" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z164" s="15">
+        <f>_xlfn.XLOOKUP(A164,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>268044</v>
+      </c>
+    </row>
+    <row r="165" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="8">
         <v>368004</v>
       </c>
-      <c r="B165" s="33" t="s">
+      <c r="B165" s="31" t="s">
         <v>1176</v>
       </c>
       <c r="C165" s="9" t="s">
@@ -21338,12 +21857,16 @@
         <v>33</v>
       </c>
       <c r="Y165" s="9"/>
-    </row>
-    <row r="166" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z165" s="15">
+        <f>_xlfn.XLOOKUP(A165,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>368004</v>
+      </c>
+    </row>
+    <row r="166" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="8">
         <v>269040</v>
       </c>
-      <c r="B166" s="33" t="s">
+      <c r="B166" s="31" t="s">
         <v>1182</v>
       </c>
       <c r="C166" s="9" t="s">
@@ -21401,12 +21924,16 @@
         <v>33</v>
       </c>
       <c r="Y166" s="9"/>
-    </row>
-    <row r="167" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z166" s="15">
+        <f>_xlfn.XLOOKUP(A166,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>269040</v>
+      </c>
+    </row>
+    <row r="167" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="B167" s="33" t="s">
+      <c r="B167" s="31" t="s">
         <v>1190</v>
       </c>
       <c r="C167" s="9" t="s">
@@ -21466,8 +21993,12 @@
         <v>57</v>
       </c>
       <c r="Y167" s="9"/>
-    </row>
-    <row r="168" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z167" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A167,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>149024 A</v>
+      </c>
+    </row>
+    <row r="168" spans="1:26" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="8">
         <v>268029</v>
       </c>
@@ -21529,8 +22060,12 @@
       <c r="Y168" s="9" t="s">
         <v>1203</v>
       </c>
-    </row>
-    <row r="169" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z168" s="15" t="e">
+        <f>_xlfn.XLOOKUP(A168,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="169" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="8">
         <v>232027</v>
       </c>
@@ -21594,8 +22129,12 @@
         <v>57</v>
       </c>
       <c r="Y169" s="9"/>
-    </row>
-    <row r="170" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z169" s="15">
+        <f>_xlfn.XLOOKUP(A169,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>232027</v>
+      </c>
+    </row>
+    <row r="170" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="16">
         <v>234092</v>
       </c>
@@ -21660,7 +22199,7 @@
       </c>
       <c r="Y170" s="9"/>
     </row>
-    <row r="171" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="16">
         <v>240029</v>
       </c>
@@ -21725,7 +22264,7 @@
       </c>
       <c r="Y171" s="9"/>
     </row>
-    <row r="172" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="16">
         <v>247012</v>
       </c>
@@ -21790,7 +22329,7 @@
       </c>
       <c r="Y172" s="9"/>
     </row>
-    <row r="173" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="16">
         <v>434007</v>
       </c>
@@ -21855,7 +22394,7 @@
       </c>
       <c r="Y173" s="9"/>
     </row>
-    <row r="174" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="16">
         <v>435004</v>
       </c>
@@ -21920,7 +22459,7 @@
       </c>
       <c r="Y174" s="9"/>
     </row>
-    <row r="175" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="16">
         <v>442002</v>
       </c>
@@ -21985,7 +22524,7 @@
       </c>
       <c r="Y175" s="9"/>
     </row>
-    <row r="176" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="16">
         <v>442007</v>
       </c>
@@ -22050,7 +22589,7 @@
       </c>
       <c r="Y176" s="9"/>
     </row>
-    <row r="177" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="8">
         <v>256029</v>
       </c>
@@ -22114,8 +22653,12 @@
         <v>57</v>
       </c>
       <c r="Y177" s="9"/>
-    </row>
-    <row r="178" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z177" s="15">
+        <f>_xlfn.XLOOKUP(A177,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>256029</v>
+      </c>
+    </row>
+    <row r="178" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="16">
         <v>269012</v>
       </c>
@@ -22176,7 +22719,7 @@
       </c>
       <c r="Y178" s="9"/>
     </row>
-    <row r="179" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="8">
         <v>236012</v>
       </c>
@@ -22240,8 +22783,12 @@
         <v>56</v>
       </c>
       <c r="Y179" s="9"/>
-    </row>
-    <row r="180" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z179" s="15">
+        <f>_xlfn.XLOOKUP(A179,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>236012</v>
+      </c>
+    </row>
+    <row r="180" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="16">
         <v>240005</v>
       </c>
@@ -22306,7 +22853,7 @@
       </c>
       <c r="Y180" s="9"/>
     </row>
-    <row r="181" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="16">
         <v>258001</v>
       </c>
@@ -22371,7 +22918,7 @@
       </c>
       <c r="Y181" s="9"/>
     </row>
-    <row r="182" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="16">
         <v>264066</v>
       </c>
@@ -22436,7 +22983,7 @@
       </c>
       <c r="Y182" s="9"/>
     </row>
-    <row r="183" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="16">
         <v>266086</v>
       </c>
@@ -22499,7 +23046,7 @@
       </c>
       <c r="Y183" s="9"/>
     </row>
-    <row r="184" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="28">
         <v>239024</v>
       </c>
@@ -22562,7 +23109,7 @@
       </c>
       <c r="Y184" s="9"/>
     </row>
-    <row r="185" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="16">
         <v>251010</v>
       </c>
@@ -22619,7 +23166,7 @@
       </c>
       <c r="Y185" s="9"/>
     </row>
-    <row r="186" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="16">
         <v>256050</v>
       </c>
@@ -22676,7 +23223,7 @@
       </c>
       <c r="Y186" s="9"/>
     </row>
-    <row r="187" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="16">
         <v>256051</v>
       </c>
@@ -22733,7 +23280,7 @@
       </c>
       <c r="Y187" s="9"/>
     </row>
-    <row r="188" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="16">
         <v>258031</v>
       </c>
@@ -22790,7 +23337,7 @@
       </c>
       <c r="Y188" s="9"/>
     </row>
-    <row r="189" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="16">
         <v>258041</v>
       </c>
@@ -22847,7 +23394,7 @@
       </c>
       <c r="Y189" s="9"/>
     </row>
-    <row r="190" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="16">
         <v>264067</v>
       </c>
@@ -22902,7 +23449,7 @@
       </c>
       <c r="Y190" s="9"/>
     </row>
-    <row r="191" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="16">
         <v>266047</v>
       </c>
@@ -22957,7 +23504,7 @@
       </c>
       <c r="Y191" s="9"/>
     </row>
-    <row r="192" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="16">
         <v>242029</v>
       </c>
@@ -23018,7 +23565,7 @@
       </c>
       <c r="Y192" s="9"/>
     </row>
-    <row r="193" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="16">
         <v>245012</v>
       </c>
@@ -23079,7 +23626,7 @@
       </c>
       <c r="Y193" s="9"/>
     </row>
-    <row r="194" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="16">
         <v>251041</v>
       </c>
@@ -23138,7 +23685,7 @@
       </c>
       <c r="Y194" s="9"/>
     </row>
-    <row r="195" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="16">
         <v>264070</v>
       </c>
@@ -23193,7 +23740,7 @@
       </c>
       <c r="Y195" s="9"/>
     </row>
-    <row r="196" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="16">
         <v>267007</v>
       </c>
@@ -23248,7 +23795,7 @@
       </c>
       <c r="Y196" s="9"/>
     </row>
-    <row r="197" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="16">
         <v>440018</v>
       </c>
@@ -23311,7 +23858,7 @@
       </c>
       <c r="Y197" s="9"/>
     </row>
-    <row r="198" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="16">
         <v>251012</v>
       </c>
@@ -23370,7 +23917,7 @@
       </c>
       <c r="Y198" s="9"/>
     </row>
-    <row r="199" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="16">
         <v>265032</v>
       </c>
@@ -23427,7 +23974,7 @@
       </c>
       <c r="Y199" s="9"/>
     </row>
-    <row r="200" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="16">
         <v>265053</v>
       </c>
@@ -23482,7 +24029,7 @@
       </c>
       <c r="Y200" s="9"/>
     </row>
-    <row r="201" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="16">
         <v>268090</v>
       </c>
@@ -23541,7 +24088,7 @@
       </c>
       <c r="Y201" s="9"/>
     </row>
-    <row r="202" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="8">
         <v>250042</v>
       </c>
@@ -23601,8 +24148,12 @@
         <v>57</v>
       </c>
       <c r="Y202" s="9"/>
-    </row>
-    <row r="203" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z202" s="15">
+        <f>_xlfn.XLOOKUP(A202,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>250042</v>
+      </c>
+    </row>
+    <row r="203" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="16">
         <v>252013</v>
       </c>
@@ -23663,7 +24214,7 @@
       </c>
       <c r="Y203" s="9"/>
     </row>
-    <row r="204" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="16">
         <v>253045</v>
       </c>
@@ -23722,7 +24273,7 @@
       </c>
       <c r="Y204" s="9"/>
     </row>
-    <row r="205" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="16">
         <v>264063</v>
       </c>
@@ -23777,7 +24328,7 @@
       </c>
       <c r="Y205" s="9"/>
     </row>
-    <row r="206" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="16">
         <v>267008</v>
       </c>
@@ -23832,7 +24383,7 @@
       </c>
       <c r="Y206" s="9"/>
     </row>
-    <row r="207" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="16">
         <v>438016</v>
       </c>
@@ -23893,7 +24444,7 @@
       </c>
       <c r="Y207" s="9"/>
     </row>
-    <row r="208" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="8">
         <v>239006</v>
       </c>
@@ -23959,8 +24510,12 @@
         <v>57</v>
       </c>
       <c r="Y208" s="9"/>
-    </row>
-    <row r="209" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z208" s="15">
+        <f>_xlfn.XLOOKUP(A208,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>239006</v>
+      </c>
+    </row>
+    <row r="209" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="8">
         <v>233034</v>
       </c>
@@ -24022,8 +24577,12 @@
         <v>57</v>
       </c>
       <c r="Y209" s="9"/>
-    </row>
-    <row r="210" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z209" s="15">
+        <f>_xlfn.XLOOKUP(A209,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>233034</v>
+      </c>
+    </row>
+    <row r="210" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="16">
         <v>240034</v>
       </c>
@@ -24088,7 +24647,7 @@
       </c>
       <c r="Y210" s="9"/>
     </row>
-    <row r="211" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="16">
         <v>245015</v>
       </c>
@@ -24153,7 +24712,7 @@
       </c>
       <c r="Y211" s="9"/>
     </row>
-    <row r="212" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="16">
         <v>247008</v>
       </c>
@@ -24218,7 +24777,7 @@
       </c>
       <c r="Y212" s="9"/>
     </row>
-    <row r="213" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="16">
         <v>249019</v>
       </c>
@@ -24283,7 +24842,7 @@
       </c>
       <c r="Y213" s="9"/>
     </row>
-    <row r="214" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="16">
         <v>249046</v>
       </c>
@@ -24344,7 +24903,7 @@
       </c>
       <c r="Y214" s="9"/>
     </row>
-    <row r="215" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="16">
         <v>250016</v>
       </c>
@@ -24405,7 +24964,7 @@
       </c>
       <c r="Y215" s="9"/>
     </row>
-    <row r="216" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="16">
         <v>250017</v>
       </c>
@@ -24468,7 +25027,7 @@
       </c>
       <c r="Y216" s="9"/>
     </row>
-    <row r="217" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="16">
         <v>250059</v>
       </c>
@@ -24529,7 +25088,7 @@
       </c>
       <c r="Y217" s="9"/>
     </row>
-    <row r="218" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="16">
         <v>253003</v>
       </c>
@@ -24584,7 +25143,7 @@
       </c>
       <c r="Y218" s="9"/>
     </row>
-    <row r="219" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="16">
         <v>254055</v>
       </c>
@@ -24647,7 +25206,7 @@
       </c>
       <c r="Y219" s="9"/>
     </row>
-    <row r="220" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="16">
         <v>261028</v>
       </c>
@@ -24710,7 +25269,7 @@
       </c>
       <c r="Y220" s="9"/>
     </row>
-    <row r="221" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="16">
         <v>264007</v>
       </c>
@@ -24773,7 +25332,7 @@
       </c>
       <c r="Y221" s="9"/>
     </row>
-    <row r="222" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="16">
         <v>265019</v>
       </c>
@@ -24838,7 +25397,7 @@
       </c>
       <c r="Y222" s="9"/>
     </row>
-    <row r="223" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="16">
         <v>265047</v>
       </c>
@@ -24901,7 +25460,7 @@
       </c>
       <c r="Y223" s="9"/>
     </row>
-    <row r="224" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="16">
         <v>266010</v>
       </c>
@@ -24960,7 +25519,7 @@
       </c>
       <c r="Y224" s="9"/>
     </row>
-    <row r="225" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="16">
         <v>266052</v>
       </c>
@@ -25019,7 +25578,7 @@
       </c>
       <c r="Y225" s="9"/>
     </row>
-    <row r="226" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="16">
         <v>266060</v>
       </c>
@@ -25078,7 +25637,7 @@
       </c>
       <c r="Y226" s="9"/>
     </row>
-    <row r="227" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="16">
         <v>267047</v>
       </c>
@@ -25137,7 +25696,7 @@
       </c>
       <c r="Y227" s="9"/>
     </row>
-    <row r="228" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="8">
         <v>268013</v>
       </c>
@@ -25199,8 +25758,12 @@
         <v>33</v>
       </c>
       <c r="Y228" s="9"/>
-    </row>
-    <row r="229" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z228" s="15">
+        <f>_xlfn.XLOOKUP(A228,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>268013</v>
+      </c>
+    </row>
+    <row r="229" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="16">
         <v>268056</v>
       </c>
@@ -25259,7 +25822,7 @@
       </c>
       <c r="Y229" s="9"/>
     </row>
-    <row r="230" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="16">
         <v>244005</v>
       </c>
@@ -25320,7 +25883,7 @@
       </c>
       <c r="Y230" s="9"/>
     </row>
-    <row r="231" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="16">
         <v>259005</v>
       </c>
@@ -25381,7 +25944,7 @@
       </c>
       <c r="Y231" s="9"/>
     </row>
-    <row r="232" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="16">
         <v>260003</v>
       </c>
@@ -25440,7 +26003,7 @@
       </c>
       <c r="Y232" s="9"/>
     </row>
-    <row r="233" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="16">
         <v>267003</v>
       </c>
@@ -25497,7 +26060,7 @@
       </c>
       <c r="Y233" s="9"/>
     </row>
-    <row r="234" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="16">
         <v>268083</v>
       </c>
@@ -25558,7 +26121,7 @@
       </c>
       <c r="Y234" s="9"/>
     </row>
-    <row r="235" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="16">
         <v>233010</v>
       </c>
@@ -25621,7 +26184,7 @@
       </c>
       <c r="Y235" s="9"/>
     </row>
-    <row r="236" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="16">
         <v>259013</v>
       </c>
@@ -25684,7 +26247,7 @@
       </c>
       <c r="Y236" s="9"/>
     </row>
-    <row r="237" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="16">
         <v>268091</v>
       </c>
@@ -25743,7 +26306,7 @@
       </c>
       <c r="Y237" s="9"/>
     </row>
-    <row r="238" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="16">
         <v>248035</v>
       </c>
@@ -25808,7 +26371,7 @@
       </c>
       <c r="Y238" s="9"/>
     </row>
-    <row r="239" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="8">
         <v>249010</v>
       </c>
@@ -25874,8 +26437,12 @@
         <v>57</v>
       </c>
       <c r="Y239" s="9"/>
-    </row>
-    <row r="240" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z239" s="15">
+        <f>_xlfn.XLOOKUP(A239,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>249010</v>
+      </c>
+    </row>
+    <row r="240" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="16">
         <v>249053</v>
       </c>
@@ -25940,7 +26507,7 @@
       </c>
       <c r="Y240" s="9"/>
     </row>
-    <row r="241" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="16">
         <v>251019</v>
       </c>
@@ -26003,7 +26570,7 @@
       </c>
       <c r="Y241" s="9"/>
     </row>
-    <row r="242" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="16">
         <v>252004</v>
       </c>
@@ -26068,7 +26635,7 @@
       </c>
       <c r="Y242" s="9"/>
     </row>
-    <row r="243" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="16">
         <v>252009</v>
       </c>
@@ -26129,7 +26696,7 @@
       </c>
       <c r="Y243" s="9"/>
     </row>
-    <row r="244" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="16">
         <v>253037</v>
       </c>
@@ -26190,7 +26757,7 @@
       </c>
       <c r="Y244" s="9"/>
     </row>
-    <row r="245" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="16">
         <v>254018</v>
       </c>
@@ -26249,7 +26816,7 @@
       </c>
       <c r="Y245" s="9"/>
     </row>
-    <row r="246" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="16">
         <v>254035</v>
       </c>
@@ -26312,7 +26879,7 @@
       </c>
       <c r="Y246" s="9"/>
     </row>
-    <row r="247" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="16">
         <v>254049</v>
       </c>
@@ -26373,7 +26940,7 @@
       </c>
       <c r="Y247" s="9"/>
     </row>
-    <row r="248" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="16">
         <v>256032</v>
       </c>
@@ -26436,7 +27003,7 @@
       </c>
       <c r="Y248" s="9"/>
     </row>
-    <row r="249" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="16">
         <v>260018</v>
       </c>
@@ -26497,7 +27064,7 @@
       </c>
       <c r="Y249" s="9"/>
     </row>
-    <row r="250" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="16">
         <v>260045</v>
       </c>
@@ -26558,7 +27125,7 @@
       </c>
       <c r="Y250" s="9"/>
     </row>
-    <row r="251" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="16">
         <v>264040</v>
       </c>
@@ -26619,7 +27186,7 @@
       </c>
       <c r="Y251" s="9"/>
     </row>
-    <row r="252" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="16">
         <v>264091</v>
       </c>
@@ -26680,7 +27247,7 @@
       </c>
       <c r="Y252" s="9"/>
     </row>
-    <row r="253" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="16">
         <v>265012</v>
       </c>
@@ -26739,7 +27306,7 @@
       </c>
       <c r="Y253" s="9"/>
     </row>
-    <row r="254" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="16">
         <v>265040</v>
       </c>
@@ -26798,7 +27365,7 @@
       </c>
       <c r="Y254" s="9"/>
     </row>
-    <row r="255" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="16">
         <v>266072</v>
       </c>
@@ -26857,7 +27424,7 @@
       </c>
       <c r="Y255" s="9"/>
     </row>
-    <row r="256" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="16">
         <v>267022</v>
       </c>
@@ -26916,7 +27483,7 @@
       </c>
       <c r="Y256" s="9"/>
     </row>
-    <row r="257" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="16">
         <v>267035</v>
       </c>
@@ -26977,7 +27544,7 @@
       </c>
       <c r="Y257" s="9"/>
     </row>
-    <row r="258" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="16">
         <v>267074</v>
       </c>
@@ -27038,7 +27605,7 @@
       </c>
       <c r="Y258" s="9"/>
     </row>
-    <row r="259" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="16">
         <v>267083</v>
       </c>
@@ -27097,7 +27664,7 @@
       </c>
       <c r="Y259" s="9"/>
     </row>
-    <row r="260" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="16">
         <v>267099</v>
       </c>
@@ -27156,7 +27723,7 @@
       </c>
       <c r="Y260" s="9"/>
     </row>
-    <row r="261" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="8">
         <v>268012</v>
       </c>
@@ -27218,8 +27785,12 @@
         <v>33</v>
       </c>
       <c r="Y261" s="9"/>
-    </row>
-    <row r="262" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z261" s="15">
+        <f>_xlfn.XLOOKUP(A261,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>268012</v>
+      </c>
+    </row>
+    <row r="262" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="16">
         <v>268042</v>
       </c>
@@ -27278,7 +27849,7 @@
       </c>
       <c r="Y262" s="9"/>
     </row>
-    <row r="263" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="16">
         <v>268073</v>
       </c>
@@ -27337,7 +27908,7 @@
       </c>
       <c r="Y263" s="9"/>
     </row>
-    <row r="264" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="16">
         <v>269024</v>
       </c>
@@ -27396,7 +27967,7 @@
       </c>
       <c r="Y264" s="9"/>
     </row>
-    <row r="265" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="8">
         <v>238030</v>
       </c>
@@ -27462,8 +28033,12 @@
         <v>57</v>
       </c>
       <c r="Y265" s="9"/>
-    </row>
-    <row r="266" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z265" s="15">
+        <f>_xlfn.XLOOKUP(A265,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>238030</v>
+      </c>
+    </row>
+    <row r="266" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="16">
         <v>240018</v>
       </c>
@@ -27526,7 +28101,7 @@
       </c>
       <c r="Y266" s="9"/>
     </row>
-    <row r="267" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="16">
         <v>251006</v>
       </c>
@@ -27591,7 +28166,7 @@
       </c>
       <c r="Y267" s="9"/>
     </row>
-    <row r="268" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="16">
         <v>251025</v>
       </c>
@@ -27654,7 +28229,7 @@
       </c>
       <c r="Y268" s="9"/>
     </row>
-    <row r="269" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="16">
         <v>252027</v>
       </c>
@@ -27719,7 +28294,7 @@
       </c>
       <c r="Y269" s="9"/>
     </row>
-    <row r="270" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="16">
         <v>253042</v>
       </c>
@@ -27782,7 +28357,7 @@
       </c>
       <c r="Y270" s="9"/>
     </row>
-    <row r="271" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="16">
         <v>256036</v>
       </c>
@@ -27843,7 +28418,7 @@
       </c>
       <c r="Y271" s="9"/>
     </row>
-    <row r="272" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="16">
         <v>256038</v>
       </c>
@@ -27904,7 +28479,7 @@
       </c>
       <c r="Y272" s="9"/>
     </row>
-    <row r="273" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="16">
         <v>266057</v>
       </c>
@@ -27967,7 +28542,7 @@
       </c>
       <c r="Y273" s="9"/>
     </row>
-    <row r="274" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="16">
         <v>266065</v>
       </c>
@@ -28026,7 +28601,7 @@
       </c>
       <c r="Y274" s="9"/>
     </row>
-    <row r="275" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="8">
         <v>246004</v>
       </c>
@@ -28092,8 +28667,12 @@
         <v>57</v>
       </c>
       <c r="Y275" s="9"/>
-    </row>
-    <row r="276" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z275" s="15">
+        <f>_xlfn.XLOOKUP(A275,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>246004</v>
+      </c>
+    </row>
+    <row r="276" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="8">
         <v>256014</v>
       </c>
@@ -28159,8 +28738,12 @@
         <v>57</v>
       </c>
       <c r="Y276" s="9"/>
-    </row>
-    <row r="277" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z276" s="15">
+        <f>_xlfn.XLOOKUP(A276,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>256014</v>
+      </c>
+    </row>
+    <row r="277" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="16">
         <v>244028</v>
       </c>
@@ -28223,7 +28806,7 @@
       </c>
       <c r="Y277" s="9"/>
     </row>
-    <row r="278" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="16">
         <v>251048</v>
       </c>
@@ -28286,7 +28869,7 @@
       </c>
       <c r="Y278" s="9"/>
     </row>
-    <row r="279" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="16">
         <v>255003</v>
       </c>
@@ -28347,7 +28930,7 @@
       </c>
       <c r="Y279" s="9"/>
     </row>
-    <row r="280" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="16">
         <v>257021</v>
       </c>
@@ -28410,7 +28993,7 @@
       </c>
       <c r="Y280" s="9"/>
     </row>
-    <row r="281" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="16">
         <v>258035</v>
       </c>
@@ -28471,7 +29054,7 @@
       </c>
       <c r="Y281" s="9"/>
     </row>
-    <row r="282" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="16">
         <v>260029</v>
       </c>
@@ -28530,7 +29113,7 @@
       </c>
       <c r="Y282" s="9"/>
     </row>
-    <row r="283" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="16">
         <v>264019</v>
       </c>
@@ -28589,7 +29172,7 @@
       </c>
       <c r="Y283" s="9"/>
     </row>
-    <row r="284" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="16">
         <v>264039</v>
       </c>
@@ -28650,7 +29233,7 @@
       </c>
       <c r="Y284" s="9"/>
     </row>
-    <row r="285" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="16">
         <v>265043</v>
       </c>
@@ -28705,7 +29288,7 @@
       </c>
       <c r="Y285" s="9"/>
     </row>
-    <row r="286" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="16">
         <v>265058</v>
       </c>
@@ -28760,7 +29343,7 @@
       </c>
       <c r="Y286" s="9"/>
     </row>
-    <row r="287" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="16">
         <v>267017</v>
       </c>
@@ -28815,7 +29398,7 @@
       </c>
       <c r="Y287" s="9"/>
     </row>
-    <row r="288" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="16">
         <v>267080</v>
       </c>
@@ -28870,7 +29453,7 @@
       </c>
       <c r="Y288" s="9"/>
     </row>
-    <row r="289" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="16">
         <v>243010</v>
       </c>
@@ -28931,7 +29514,7 @@
       </c>
       <c r="Y289" s="9"/>
     </row>
-    <row r="290" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="16">
         <v>255004</v>
       </c>
@@ -28992,7 +29575,7 @@
       </c>
       <c r="Y290" s="9"/>
     </row>
-    <row r="291" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="16">
         <v>258022</v>
       </c>
@@ -29053,7 +29636,7 @@
       </c>
       <c r="Y291" s="9"/>
     </row>
-    <row r="292" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="16">
         <v>265023</v>
       </c>
@@ -29108,7 +29691,7 @@
       </c>
       <c r="Y292" s="9"/>
     </row>
-    <row r="293" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="16">
         <v>267005</v>
       </c>
@@ -29163,7 +29746,7 @@
       </c>
       <c r="Y293" s="9"/>
     </row>
-    <row r="294" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="16">
         <v>267060</v>
       </c>
@@ -29222,7 +29805,7 @@
       </c>
       <c r="Y294" s="9"/>
     </row>
-    <row r="295" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="16">
         <v>439003</v>
       </c>
@@ -29283,7 +29866,7 @@
       </c>
       <c r="Y295" s="9"/>
     </row>
-    <row r="296" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="16">
         <v>244011</v>
       </c>
@@ -29344,7 +29927,7 @@
       </c>
       <c r="Y296" s="9"/>
     </row>
-    <row r="297" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="16">
         <v>247019</v>
       </c>
@@ -29407,7 +29990,7 @@
       </c>
       <c r="Y297" s="9"/>
     </row>
-    <row r="298" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="16">
         <v>252038</v>
       </c>
@@ -29470,7 +30053,7 @@
       </c>
       <c r="Y298" s="9"/>
     </row>
-    <row r="299" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="16">
         <v>259016</v>
       </c>
@@ -29531,7 +30114,7 @@
       </c>
       <c r="Y299" s="9"/>
     </row>
-    <row r="300" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="16">
         <v>264044</v>
       </c>
@@ -29592,7 +30175,7 @@
       </c>
       <c r="Y300" s="9"/>
     </row>
-    <row r="301" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="16">
         <v>264074</v>
       </c>
@@ -29649,7 +30232,7 @@
       </c>
       <c r="Y301" s="9"/>
     </row>
-    <row r="302" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="16">
         <v>264075</v>
       </c>
@@ -29706,7 +30289,7 @@
       </c>
       <c r="Y302" s="9"/>
     </row>
-    <row r="303" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="16">
         <v>265110</v>
       </c>
@@ -29761,7 +30344,7 @@
       </c>
       <c r="Y303" s="9"/>
     </row>
-    <row r="304" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="16">
         <v>266013</v>
       </c>
@@ -29816,7 +30399,7 @@
       </c>
       <c r="Y304" s="9"/>
     </row>
-    <row r="305" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="16">
         <v>267014</v>
       </c>
@@ -29871,7 +30454,7 @@
       </c>
       <c r="Y305" s="9"/>
     </row>
-    <row r="306" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="16">
         <v>267015</v>
       </c>
@@ -29926,7 +30509,7 @@
       </c>
       <c r="Y306" s="9"/>
     </row>
-    <row r="307" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="16">
         <v>267086</v>
       </c>
@@ -29985,7 +30568,7 @@
       </c>
       <c r="Y307" s="9"/>
     </row>
-    <row r="308" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="16">
         <v>268030</v>
       </c>
@@ -30044,7 +30627,7 @@
       </c>
       <c r="Y308" s="9"/>
     </row>
-    <row r="309" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="16">
         <v>268031</v>
       </c>
@@ -30103,7 +30686,7 @@
       </c>
       <c r="Y309" s="9"/>
     </row>
-    <row r="310" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="16">
         <v>268041</v>
       </c>
@@ -30162,7 +30745,7 @@
       </c>
       <c r="Y310" s="9"/>
     </row>
-    <row r="311" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="16">
         <v>257019</v>
       </c>
@@ -30223,7 +30806,7 @@
       </c>
       <c r="Y311" s="9"/>
     </row>
-    <row r="312" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="16">
         <v>242025</v>
       </c>
@@ -30288,7 +30871,7 @@
       </c>
       <c r="Y312" s="9"/>
     </row>
-    <row r="313" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="16">
         <v>243003</v>
       </c>
@@ -30353,7 +30936,7 @@
       </c>
       <c r="Y313" s="9"/>
     </row>
-    <row r="314" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="16">
         <v>247020</v>
       </c>
@@ -30414,7 +30997,7 @@
       </c>
       <c r="Y314" s="9"/>
     </row>
-    <row r="315" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="16">
         <v>249094</v>
       </c>
@@ -30477,7 +31060,7 @@
       </c>
       <c r="Y315" s="9"/>
     </row>
-    <row r="316" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="16">
         <v>257018</v>
       </c>
@@ -30540,7 +31123,7 @@
       </c>
       <c r="Y316" s="9"/>
     </row>
-    <row r="317" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="8">
         <v>443003</v>
       </c>
@@ -30606,8 +31189,12 @@
         <v>114</v>
       </c>
       <c r="Y317" s="9"/>
-    </row>
-    <row r="318" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z317" s="15">
+        <f>_xlfn.XLOOKUP(A317,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>443003</v>
+      </c>
+    </row>
+    <row r="318" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="8">
         <v>254057</v>
       </c>
@@ -30673,8 +31260,12 @@
         <v>57</v>
       </c>
       <c r="Y318" s="9"/>
-    </row>
-    <row r="319" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z318" s="15">
+        <f>_xlfn.XLOOKUP(A318,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>254057</v>
+      </c>
+    </row>
+    <row r="319" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="8">
         <v>237011</v>
       </c>
@@ -30740,8 +31331,12 @@
         <v>57</v>
       </c>
       <c r="Y319" s="9"/>
-    </row>
-    <row r="320" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z319" s="15">
+        <f>_xlfn.XLOOKUP(A319,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>237011</v>
+      </c>
+    </row>
+    <row r="320" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="16">
         <v>249058</v>
       </c>
@@ -30802,7 +31397,7 @@
       </c>
       <c r="Y320" s="9"/>
     </row>
-    <row r="321" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="16">
         <v>254037</v>
       </c>
@@ -30863,7 +31458,7 @@
       </c>
       <c r="Y321" s="9"/>
     </row>
-    <row r="322" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="16">
         <v>261014</v>
       </c>
@@ -30922,7 +31517,7 @@
       </c>
       <c r="Y322" s="9"/>
     </row>
-    <row r="323" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="16">
         <v>265066</v>
       </c>
@@ -30981,7 +31576,7 @@
       </c>
       <c r="Y323" s="9"/>
     </row>
-    <row r="324" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="16">
         <v>266031</v>
       </c>
@@ -31040,7 +31635,7 @@
       </c>
       <c r="Y324" s="9"/>
     </row>
-    <row r="325" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="16">
         <v>268088</v>
       </c>
@@ -31099,7 +31694,7 @@
       </c>
       <c r="Y325" s="9"/>
     </row>
-    <row r="326" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="16">
         <v>236069</v>
       </c>
@@ -31162,7 +31757,7 @@
       </c>
       <c r="Y326" s="9"/>
     </row>
-    <row r="327" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="16">
         <v>245001</v>
       </c>
@@ -31223,7 +31818,7 @@
       </c>
       <c r="Y327" s="9"/>
     </row>
-    <row r="328" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="16">
         <v>245006</v>
       </c>
@@ -31286,7 +31881,7 @@
       </c>
       <c r="Y328" s="9"/>
     </row>
-    <row r="329" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="16">
         <v>248043</v>
       </c>
@@ -31347,7 +31942,7 @@
       </c>
       <c r="Y329" s="9"/>
     </row>
-    <row r="330" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="16">
         <v>249036</v>
       </c>
@@ -31408,7 +32003,7 @@
       </c>
       <c r="Y330" s="9"/>
     </row>
-    <row r="331" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="16">
         <v>256042</v>
       </c>
@@ -31469,7 +32064,7 @@
       </c>
       <c r="Y331" s="9"/>
     </row>
-    <row r="332" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="16">
         <v>264008</v>
       </c>
@@ -31532,7 +32127,7 @@
       </c>
       <c r="Y332" s="9"/>
     </row>
-    <row r="333" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="16">
         <v>265103</v>
       </c>
@@ -31591,7 +32186,7 @@
       </c>
       <c r="Y333" s="9"/>
     </row>
-    <row r="334" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="16">
         <v>266090</v>
       </c>
@@ -31652,7 +32247,7 @@
       </c>
       <c r="Y334" s="9"/>
     </row>
-    <row r="335" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="16">
         <v>268074</v>
       </c>
@@ -31713,7 +32308,7 @@
       </c>
       <c r="Y335" s="9"/>
     </row>
-    <row r="336" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="16">
         <v>265128</v>
       </c>
@@ -31772,7 +32367,7 @@
       </c>
       <c r="Y336" s="9"/>
     </row>
-    <row r="337" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="16">
         <v>267052</v>
       </c>
@@ -31827,7 +32422,7 @@
       </c>
       <c r="Y337" s="9"/>
     </row>
-    <row r="338" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="16">
         <v>268028</v>
       </c>
@@ -31886,7 +32481,7 @@
       </c>
       <c r="Y338" s="9"/>
     </row>
-    <row r="339" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="16">
         <v>268053</v>
       </c>
@@ -31945,7 +32540,7 @@
       </c>
       <c r="Y339" s="9"/>
     </row>
-    <row r="340" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="16">
         <v>268062</v>
       </c>
@@ -32004,7 +32599,7 @@
       </c>
       <c r="Y340" s="9"/>
     </row>
-    <row r="341" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="16">
         <v>268076</v>
       </c>
@@ -32063,7 +32658,7 @@
       </c>
       <c r="Y341" s="9"/>
     </row>
-    <row r="342" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="16">
         <v>269003</v>
       </c>
@@ -32122,7 +32717,7 @@
       </c>
       <c r="Y342" s="9"/>
     </row>
-    <row r="343" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="16">
         <v>269006</v>
       </c>
@@ -32181,7 +32776,7 @@
       </c>
       <c r="Y343" s="9"/>
     </row>
-    <row r="344" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="16">
         <v>269018</v>
       </c>
@@ -32240,7 +32835,7 @@
       </c>
       <c r="Y344" s="9"/>
     </row>
-    <row r="345" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="16">
         <v>269019</v>
       </c>
@@ -32299,7 +32894,7 @@
       </c>
       <c r="Y345" s="9"/>
     </row>
-    <row r="346" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="16">
         <v>249086</v>
       </c>
@@ -32360,7 +32955,7 @@
       </c>
       <c r="Y346" s="9"/>
     </row>
-    <row r="347" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="8">
         <v>267096</v>
       </c>
@@ -32422,8 +33017,12 @@
         <v>33</v>
       </c>
       <c r="Y347" s="9"/>
-    </row>
-    <row r="348" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z347" s="15">
+        <f>_xlfn.XLOOKUP(A347,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>267096</v>
+      </c>
+    </row>
+    <row r="348" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="16">
         <v>250062</v>
       </c>
@@ -32488,7 +33087,7 @@
       </c>
       <c r="Y348" s="9"/>
     </row>
-    <row r="349" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="16">
         <v>256015</v>
       </c>
@@ -32549,7 +33148,7 @@
       </c>
       <c r="Y349" s="9"/>
     </row>
-    <row r="350" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="16">
         <v>256016</v>
       </c>
@@ -32612,7 +33211,7 @@
       </c>
       <c r="Y350" s="9"/>
     </row>
-    <row r="351" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="16">
         <v>259024</v>
       </c>
@@ -32675,7 +33274,7 @@
       </c>
       <c r="Y351" s="9"/>
     </row>
-    <row r="352" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="16">
         <v>264045</v>
       </c>
@@ -32734,7 +33333,7 @@
       </c>
       <c r="Y352" s="9"/>
     </row>
-    <row r="353" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="16">
         <v>265111</v>
       </c>
@@ -32793,7 +33392,7 @@
       </c>
       <c r="Y353" s="9"/>
     </row>
-    <row r="354" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="16">
         <v>265124</v>
       </c>
@@ -32852,7 +33451,7 @@
       </c>
       <c r="Y354" s="9"/>
     </row>
-    <row r="355" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="16">
         <v>266030</v>
       </c>
@@ -32911,7 +33510,7 @@
       </c>
       <c r="Y355" s="9"/>
     </row>
-    <row r="356" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="16">
         <v>251029</v>
       </c>
@@ -32972,7 +33571,7 @@
       </c>
       <c r="Y356" s="9"/>
     </row>
-    <row r="357" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="16">
         <v>256004</v>
       </c>
@@ -33033,7 +33632,7 @@
       </c>
       <c r="Y357" s="9"/>
     </row>
-    <row r="358" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="16">
         <v>264022</v>
       </c>
@@ -33092,7 +33691,7 @@
       </c>
       <c r="Y358" s="9"/>
     </row>
-    <row r="359" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="16">
         <v>264083</v>
       </c>
@@ -33155,7 +33754,7 @@
       </c>
       <c r="Y359" s="9"/>
     </row>
-    <row r="360" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="16">
         <v>265010</v>
       </c>
@@ -33214,7 +33813,7 @@
       </c>
       <c r="Y360" s="9"/>
     </row>
-    <row r="361" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="16">
         <v>265013</v>
       </c>
@@ -33275,7 +33874,7 @@
       </c>
       <c r="Y361" s="9"/>
     </row>
-    <row r="362" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="16">
         <v>251050</v>
       </c>
@@ -33338,7 +33937,7 @@
       </c>
       <c r="Y362" s="9"/>
     </row>
-    <row r="363" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="16">
         <v>251058</v>
       </c>
@@ -33399,7 +33998,7 @@
       </c>
       <c r="Y363" s="9"/>
     </row>
-    <row r="364" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="16">
         <v>251062</v>
       </c>
@@ -33460,7 +34059,7 @@
       </c>
       <c r="Y364" s="9"/>
     </row>
-    <row r="365" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="16">
         <v>259022</v>
       </c>
@@ -33523,7 +34122,7 @@
       </c>
       <c r="Y365" s="9"/>
     </row>
-    <row r="366" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="16">
         <v>259038</v>
       </c>
@@ -33584,7 +34183,7 @@
       </c>
       <c r="Y366" s="9"/>
     </row>
-    <row r="367" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="16">
         <v>264048</v>
       </c>
@@ -33643,7 +34242,7 @@
       </c>
       <c r="Y367" s="9"/>
     </row>
-    <row r="368" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="16">
         <v>264051</v>
       </c>
@@ -33702,7 +34301,7 @@
       </c>
       <c r="Y368" s="9"/>
     </row>
-    <row r="369" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="16">
         <v>264089</v>
       </c>
@@ -33761,7 +34360,7 @@
       </c>
       <c r="Y369" s="9"/>
     </row>
-    <row r="370" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="16">
         <v>265061</v>
       </c>
@@ -33820,7 +34419,7 @@
       </c>
       <c r="Y370" s="9"/>
     </row>
-    <row r="371" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="16">
         <v>265076</v>
       </c>
@@ -33879,7 +34478,7 @@
       </c>
       <c r="Y371" s="9"/>
     </row>
-    <row r="372" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="16">
         <v>266037</v>
       </c>
@@ -33938,7 +34537,7 @@
       </c>
       <c r="Y372" s="9"/>
     </row>
-    <row r="373" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="16">
         <v>441005</v>
       </c>
@@ -34003,7 +34602,7 @@
       </c>
       <c r="Y373" s="9"/>
     </row>
-    <row r="374" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="16">
         <v>268037</v>
       </c>
@@ -34062,7 +34661,7 @@
       </c>
       <c r="Y374" s="9"/>
     </row>
-    <row r="375" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="16">
         <v>250022</v>
       </c>
@@ -34125,7 +34724,7 @@
       </c>
       <c r="Y375" s="9"/>
     </row>
-    <row r="376" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="16">
         <v>251028</v>
       </c>
@@ -34186,7 +34785,7 @@
       </c>
       <c r="Y376" s="9"/>
     </row>
-    <row r="377" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="16">
         <v>253023</v>
       </c>
@@ -34247,7 +34846,7 @@
       </c>
       <c r="Y377" s="9"/>
     </row>
-    <row r="378" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="16">
         <v>264084</v>
       </c>
@@ -34308,7 +34907,7 @@
       </c>
       <c r="Y378" s="9"/>
     </row>
-    <row r="379" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="16">
         <v>265127</v>
       </c>
@@ -34367,7 +34966,7 @@
       </c>
       <c r="Y379" s="9"/>
     </row>
-    <row r="380" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="16">
         <v>266016</v>
       </c>
@@ -34426,7 +35025,7 @@
       </c>
       <c r="Y380" s="9"/>
     </row>
-    <row r="381" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="16">
         <v>247007</v>
       </c>
@@ -34487,7 +35086,7 @@
       </c>
       <c r="Y381" s="9"/>
     </row>
-    <row r="382" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="16">
         <v>251002</v>
       </c>
@@ -34550,7 +35149,7 @@
       </c>
       <c r="Y382" s="9"/>
     </row>
-    <row r="383" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="16">
         <v>251023</v>
       </c>
@@ -34611,7 +35210,7 @@
       </c>
       <c r="Y383" s="9"/>
     </row>
-    <row r="384" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="16">
         <v>262008</v>
       </c>
@@ -34672,7 +35271,7 @@
       </c>
       <c r="Y384" s="9"/>
     </row>
-    <row r="385" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="16">
         <v>265063</v>
       </c>
@@ -34731,7 +35330,7 @@
       </c>
       <c r="Y385" s="9"/>
     </row>
-    <row r="386" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="16">
         <v>266002</v>
       </c>
@@ -34790,7 +35389,7 @@
       </c>
       <c r="Y386" s="9"/>
     </row>
-    <row r="387" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="16">
         <v>246013</v>
       </c>
@@ -34851,7 +35450,7 @@
       </c>
       <c r="Y387" s="9"/>
     </row>
-    <row r="388" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="8">
         <v>249048</v>
       </c>
@@ -34917,8 +35516,12 @@
         <v>57</v>
       </c>
       <c r="Y388" s="9"/>
-    </row>
-    <row r="389" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z388" s="15">
+        <f>_xlfn.XLOOKUP(A388,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>249048</v>
+      </c>
+    </row>
+    <row r="389" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="16">
         <v>250010</v>
       </c>
@@ -34979,7 +35582,7 @@
       </c>
       <c r="Y389" s="9"/>
     </row>
-    <row r="390" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="16">
         <v>251065</v>
       </c>
@@ -35040,7 +35643,7 @@
       </c>
       <c r="Y390" s="9"/>
     </row>
-    <row r="391" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="16">
         <v>265126</v>
       </c>
@@ -35103,7 +35706,7 @@
       </c>
       <c r="Y391" s="9"/>
     </row>
-    <row r="392" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="16">
         <v>267043</v>
       </c>
@@ -35162,7 +35765,7 @@
       </c>
       <c r="Y392" s="9"/>
     </row>
-    <row r="393" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="16">
         <v>267072</v>
       </c>
@@ -35223,7 +35826,7 @@
       </c>
       <c r="Y393" s="9"/>
     </row>
-    <row r="394" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="16">
         <v>467004</v>
       </c>
@@ -35282,7 +35885,7 @@
       </c>
       <c r="Y394" s="9"/>
     </row>
-    <row r="395" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="16">
         <v>467005</v>
       </c>
@@ -35341,7 +35944,7 @@
       </c>
       <c r="Y395" s="9"/>
     </row>
-    <row r="396" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="8">
         <v>242032</v>
       </c>
@@ -35407,8 +36010,12 @@
         <v>57</v>
       </c>
       <c r="Y396" s="9"/>
-    </row>
-    <row r="397" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z396" s="15">
+        <f>_xlfn.XLOOKUP(A396,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>242032</v>
+      </c>
+    </row>
+    <row r="397" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="16">
         <v>268052</v>
       </c>
@@ -35469,7 +36076,7 @@
       </c>
       <c r="Y397" s="9"/>
     </row>
-    <row r="398" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="8">
         <v>269022</v>
       </c>
@@ -35531,8 +36138,12 @@
         <v>33</v>
       </c>
       <c r="Y398" s="9"/>
-    </row>
-    <row r="399" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z398" s="15">
+        <f>_xlfn.XLOOKUP(A398,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>269022</v>
+      </c>
+    </row>
+    <row r="399" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="16">
         <v>236082</v>
       </c>
@@ -35595,7 +36206,7 @@
       </c>
       <c r="Y399" s="9"/>
     </row>
-    <row r="400" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="16">
         <v>244006</v>
       </c>
@@ -35652,7 +36263,7 @@
       </c>
       <c r="Y400" s="9"/>
     </row>
-    <row r="401" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="16">
         <v>251067</v>
       </c>
@@ -35715,7 +36326,7 @@
       </c>
       <c r="Y401" s="9"/>
     </row>
-    <row r="402" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="16">
         <v>257014</v>
       </c>
@@ -35770,7 +36381,7 @@
       </c>
       <c r="Y402" s="9"/>
     </row>
-    <row r="403" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="16">
         <v>258021</v>
       </c>
@@ -35827,7 +36438,7 @@
       </c>
       <c r="Y403" s="9"/>
     </row>
-    <row r="404" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="16">
         <v>265027</v>
       </c>
@@ -35884,7 +36495,7 @@
       </c>
       <c r="Y404" s="9"/>
     </row>
-    <row r="405" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="16">
         <v>265039</v>
       </c>
@@ -35941,7 +36552,7 @@
       </c>
       <c r="Y405" s="9"/>
     </row>
-    <row r="406" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="16">
         <v>265050</v>
       </c>
@@ -35996,7 +36607,7 @@
       </c>
       <c r="Y406" s="9"/>
     </row>
-    <row r="407" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="16">
         <v>265089</v>
       </c>
@@ -36051,7 +36662,7 @@
       </c>
       <c r="Y407" s="9"/>
     </row>
-    <row r="408" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="16">
         <v>265094</v>
       </c>
@@ -36108,7 +36719,7 @@
       </c>
       <c r="Y408" s="9"/>
     </row>
-    <row r="409" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="16">
         <v>265129</v>
       </c>
@@ -36165,7 +36776,7 @@
       </c>
       <c r="Y409" s="9"/>
     </row>
-    <row r="410" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="16">
         <v>266068</v>
       </c>
@@ -36220,7 +36831,7 @@
       </c>
       <c r="Y410" s="9"/>
     </row>
-    <row r="411" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="16">
         <v>267088</v>
       </c>
@@ -36275,7 +36886,7 @@
       </c>
       <c r="Y411" s="9"/>
     </row>
-    <row r="412" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="16">
         <v>267104</v>
       </c>
@@ -36330,7 +36941,7 @@
       </c>
       <c r="Y412" s="9"/>
     </row>
-    <row r="413" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="16">
         <v>268009</v>
       </c>
@@ -36385,7 +36996,7 @@
       </c>
       <c r="Y413" s="9"/>
     </row>
-    <row r="414" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="16">
         <v>268070</v>
       </c>
@@ -36444,7 +37055,7 @@
       </c>
       <c r="Y414" s="9"/>
     </row>
-    <row r="415" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="16">
         <v>268087</v>
       </c>
@@ -36503,7 +37114,7 @@
       </c>
       <c r="Y415" s="9"/>
     </row>
-    <row r="416" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="16">
         <v>257007</v>
       </c>
@@ -36558,7 +37169,7 @@
       </c>
       <c r="Y416" s="9"/>
     </row>
-    <row r="417" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="16">
         <v>257008</v>
       </c>
@@ -36613,7 +37224,7 @@
       </c>
       <c r="Y417" s="9"/>
     </row>
-    <row r="418" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="16">
         <v>257009</v>
       </c>
@@ -36676,7 +37287,7 @@
       </c>
       <c r="Y418" s="9"/>
     </row>
-    <row r="419" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="16">
         <v>264011</v>
       </c>
@@ -36733,7 +37344,7 @@
       </c>
       <c r="Y419" s="9"/>
     </row>
-    <row r="420" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="16">
         <v>268055</v>
       </c>
@@ -36792,7 +37403,7 @@
       </c>
       <c r="Y420" s="9"/>
     </row>
-    <row r="421" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="28">
         <v>442009</v>
       </c>
@@ -36851,7 +37462,7 @@
       </c>
       <c r="Y421" s="9"/>
     </row>
-    <row r="422" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="16">
         <v>239036</v>
       </c>
@@ -36914,7 +37525,7 @@
       </c>
       <c r="Y422" s="9"/>
     </row>
-    <row r="423" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="16">
         <v>245007</v>
       </c>
@@ -36971,7 +37582,7 @@
       </c>
       <c r="Y423" s="9"/>
     </row>
-    <row r="424" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="16">
         <v>245028</v>
       </c>
@@ -37028,7 +37639,7 @@
       </c>
       <c r="Y424" s="9"/>
     </row>
-    <row r="425" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="16">
         <v>245029</v>
       </c>
@@ -37085,7 +37696,7 @@
       </c>
       <c r="Y425" s="9"/>
     </row>
-    <row r="426" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="16">
         <v>249026</v>
       </c>
@@ -37142,7 +37753,7 @@
       </c>
       <c r="Y426" s="9"/>
     </row>
-    <row r="427" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="16">
         <v>251015</v>
       </c>
@@ -37201,7 +37812,7 @@
       </c>
       <c r="Y427" s="9"/>
     </row>
-    <row r="428" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="16">
         <v>251020</v>
       </c>
@@ -37260,7 +37871,7 @@
       </c>
       <c r="Y428" s="9"/>
     </row>
-    <row r="429" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="16">
         <v>253009</v>
       </c>
@@ -37317,7 +37928,7 @@
       </c>
       <c r="Y429" s="9"/>
     </row>
-    <row r="430" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="16">
         <v>254024</v>
       </c>
@@ -37372,7 +37983,7 @@
       </c>
       <c r="Y430" s="9"/>
     </row>
-    <row r="431" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="16">
         <v>256056</v>
       </c>
@@ -37433,7 +38044,7 @@
       </c>
       <c r="Y431" s="9"/>
     </row>
-    <row r="432" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="16">
         <v>257015</v>
       </c>
@@ -37488,7 +38099,7 @@
       </c>
       <c r="Y432" s="9"/>
     </row>
-    <row r="433" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="16">
         <v>257035</v>
       </c>
@@ -37545,7 +38156,7 @@
       </c>
       <c r="Y433" s="9"/>
     </row>
-    <row r="434" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="16">
         <v>258004</v>
       </c>
@@ -37606,7 +38217,7 @@
       </c>
       <c r="Y434" s="9"/>
     </row>
-    <row r="435" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="16">
         <v>260024</v>
       </c>
@@ -37661,7 +38272,7 @@
       </c>
       <c r="Y435" s="9"/>
     </row>
-    <row r="436" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="16">
         <v>260038</v>
       </c>
@@ -37720,7 +38331,7 @@
       </c>
       <c r="Y436" s="9"/>
     </row>
-    <row r="437" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="16">
         <v>264025</v>
       </c>
@@ -37775,7 +38386,7 @@
       </c>
       <c r="Y437" s="9"/>
     </row>
-    <row r="438" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="16">
         <v>265099</v>
       </c>
@@ -37830,7 +38441,7 @@
       </c>
       <c r="Y438" s="9"/>
     </row>
-    <row r="439" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="16">
         <v>269004</v>
       </c>
@@ -37889,7 +38500,7 @@
       </c>
       <c r="Y439" s="9"/>
     </row>
-    <row r="440" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="8">
         <v>253014</v>
       </c>
@@ -37955,8 +38566,12 @@
         <v>57</v>
       </c>
       <c r="Y440" s="9"/>
-    </row>
-    <row r="441" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z440" s="15">
+        <f>_xlfn.XLOOKUP(A440,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>253014</v>
+      </c>
+    </row>
+    <row r="441" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="16">
         <v>237017</v>
       </c>
@@ -38019,7 +38634,7 @@
       </c>
       <c r="Y441" s="9"/>
     </row>
-    <row r="442" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="16">
         <v>241015</v>
       </c>
@@ -38082,7 +38697,7 @@
       </c>
       <c r="Y442" s="9"/>
     </row>
-    <row r="443" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="16">
         <v>250056</v>
       </c>
@@ -38145,7 +38760,7 @@
       </c>
       <c r="Y443" s="9"/>
     </row>
-    <row r="444" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="16">
         <v>254061</v>
       </c>
@@ -38204,7 +38819,7 @@
       </c>
       <c r="Y444" s="9"/>
     </row>
-    <row r="445" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="16">
         <v>260041</v>
       </c>
@@ -38267,7 +38882,7 @@
       </c>
       <c r="Y445" s="9"/>
     </row>
-    <row r="446" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="16">
         <v>242017</v>
       </c>
@@ -38326,7 +38941,7 @@
       </c>
       <c r="Y446" s="9"/>
     </row>
-    <row r="447" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="16">
         <v>246006</v>
       </c>
@@ -38389,7 +39004,7 @@
       </c>
       <c r="Y447" s="9"/>
     </row>
-    <row r="448" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="16">
         <v>246010</v>
       </c>
@@ -38452,7 +39067,7 @@
       </c>
       <c r="Y448" s="9"/>
     </row>
-    <row r="449" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="16">
         <v>248013</v>
       </c>
@@ -38515,7 +39130,7 @@
       </c>
       <c r="Y449" s="9"/>
     </row>
-    <row r="450" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="16">
         <v>248039</v>
       </c>
@@ -38574,7 +39189,7 @@
       </c>
       <c r="Y450" s="9"/>
     </row>
-    <row r="451" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="16">
         <v>256067</v>
       </c>
@@ -38637,7 +39252,7 @@
       </c>
       <c r="Y451" s="9"/>
     </row>
-    <row r="452" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="16">
         <v>260048</v>
       </c>
@@ -38698,7 +39313,7 @@
       </c>
       <c r="Y452" s="9"/>
     </row>
-    <row r="453" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="16">
         <v>261005</v>
       </c>
@@ -38759,7 +39374,7 @@
       </c>
       <c r="Y453" s="9"/>
     </row>
-    <row r="454" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="16">
         <v>261037</v>
       </c>
@@ -38824,7 +39439,7 @@
       </c>
       <c r="Y454" s="9"/>
     </row>
-    <row r="455" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="16">
         <v>267018</v>
       </c>
@@ -38883,7 +39498,7 @@
       </c>
       <c r="Y455" s="9"/>
     </row>
-    <row r="456" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="16">
         <v>268045</v>
       </c>
@@ -38942,7 +39557,7 @@
       </c>
       <c r="Y456" s="9"/>
     </row>
-    <row r="457" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="8">
         <v>248031</v>
       </c>
@@ -39008,8 +39623,12 @@
         <v>57</v>
       </c>
       <c r="Y457" s="9"/>
-    </row>
-    <row r="458" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z457" s="15">
+        <f>_xlfn.XLOOKUP(A457,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>248031</v>
+      </c>
+    </row>
+    <row r="458" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="16">
         <v>268020</v>
       </c>
@@ -39070,7 +39689,7 @@
       </c>
       <c r="Y458" s="9"/>
     </row>
-    <row r="459" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="16">
         <v>268077</v>
       </c>
@@ -39131,7 +39750,7 @@
       </c>
       <c r="Y459" s="9"/>
     </row>
-    <row r="460" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="16">
         <v>233025</v>
       </c>
@@ -39194,7 +39813,7 @@
       </c>
       <c r="Y460" s="9"/>
     </row>
-    <row r="461" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="16">
         <v>265132</v>
       </c>
@@ -39257,7 +39876,7 @@
       </c>
       <c r="Y461" s="9"/>
     </row>
-    <row r="462" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="16">
         <v>266048</v>
       </c>
@@ -39318,7 +39937,7 @@
       </c>
       <c r="Y462" s="9"/>
     </row>
-    <row r="463" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="16">
         <v>266088</v>
       </c>
@@ -39375,7 +39994,7 @@
       </c>
       <c r="Y463" s="9"/>
     </row>
-    <row r="464" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="16">
         <v>469002</v>
       </c>
@@ -39436,7 +40055,7 @@
       </c>
       <c r="Y464" s="9"/>
     </row>
-    <row r="465" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="16">
         <v>268007</v>
       </c>
@@ -39495,7 +40114,7 @@
       </c>
       <c r="Y465" s="9"/>
     </row>
-    <row r="466" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="8">
         <v>251007</v>
       </c>
@@ -39561,8 +40180,12 @@
         <v>57</v>
       </c>
       <c r="Y466" s="9"/>
-    </row>
-    <row r="467" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z466" s="15">
+        <f>_xlfn.XLOOKUP(A466,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>251007</v>
+      </c>
+    </row>
+    <row r="467" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="16">
         <v>268048</v>
       </c>
@@ -39623,7 +40246,7 @@
       </c>
       <c r="Y467" s="9"/>
     </row>
-    <row r="468" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="16">
         <v>252001</v>
       </c>
@@ -39688,7 +40311,7 @@
       </c>
       <c r="Y468" s="9"/>
     </row>
-    <row r="469" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="16">
         <v>264071</v>
       </c>
@@ -39745,7 +40368,7 @@
       </c>
       <c r="Y469" s="9"/>
     </row>
-    <row r="470" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="16">
         <v>264088</v>
       </c>
@@ -39806,7 +40429,7 @@
       </c>
       <c r="Y470" s="9"/>
     </row>
-    <row r="471" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="16">
         <v>268002</v>
       </c>
@@ -39867,7 +40490,7 @@
       </c>
       <c r="Y471" s="9"/>
     </row>
-    <row r="472" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="16">
         <v>232015</v>
       </c>
@@ -39924,7 +40547,7 @@
       </c>
       <c r="Y472" s="9"/>
     </row>
-    <row r="473" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="16">
         <v>237068</v>
       </c>
@@ -39983,7 +40606,7 @@
       </c>
       <c r="Y473" s="9"/>
     </row>
-    <row r="474" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="8">
         <v>242012</v>
       </c>
@@ -40049,8 +40672,12 @@
         <v>57</v>
       </c>
       <c r="Y474" s="9"/>
-    </row>
-    <row r="475" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z474" s="15">
+        <f>_xlfn.XLOOKUP(A474,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>242012</v>
+      </c>
+    </row>
+    <row r="475" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="16">
         <v>250054</v>
       </c>
@@ -40107,7 +40734,7 @@
       </c>
       <c r="Y475" s="9"/>
     </row>
-    <row r="476" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="16">
         <v>254002</v>
       </c>
@@ -40164,7 +40791,7 @@
       </c>
       <c r="Y476" s="9"/>
     </row>
-    <row r="477" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="16">
         <v>254004</v>
       </c>
@@ -40223,7 +40850,7 @@
       </c>
       <c r="Y477" s="9"/>
     </row>
-    <row r="478" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="16">
         <v>254044</v>
       </c>
@@ -40282,7 +40909,7 @@
       </c>
       <c r="Y478" s="9"/>
     </row>
-    <row r="479" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="16">
         <v>258032</v>
       </c>
@@ -40341,7 +40968,7 @@
       </c>
       <c r="Y479" s="9"/>
     </row>
-    <row r="480" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="16">
         <v>265054</v>
       </c>
@@ -40404,7 +41031,7 @@
       </c>
       <c r="Y480" s="9"/>
     </row>
-    <row r="481" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="16">
         <v>265086</v>
       </c>
@@ -40459,7 +41086,7 @@
       </c>
       <c r="Y481" s="9"/>
     </row>
-    <row r="482" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="16">
         <v>266062</v>
       </c>
@@ -40514,7 +41141,7 @@
       </c>
       <c r="Y482" s="9"/>
     </row>
-    <row r="483" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="16">
         <v>266077</v>
       </c>
@@ -40575,7 +41202,7 @@
       </c>
       <c r="Y483" s="9"/>
     </row>
-    <row r="484" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="16">
         <v>269017</v>
       </c>
@@ -40634,7 +41261,7 @@
       </c>
       <c r="Y484" s="9"/>
     </row>
-    <row r="485" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="16">
         <v>235118</v>
       </c>
@@ -40691,7 +41318,7 @@
       </c>
       <c r="Y485" s="9"/>
     </row>
-    <row r="486" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="16">
         <v>268063</v>
       </c>
@@ -40750,7 +41377,7 @@
       </c>
       <c r="Y486" s="9"/>
     </row>
-    <row r="487" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="16">
         <v>268084</v>
       </c>
@@ -40811,7 +41438,7 @@
       </c>
       <c r="Y487" s="9"/>
     </row>
-    <row r="488" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="8">
         <v>469001</v>
       </c>
@@ -40868,7 +41495,7 @@
       </c>
       <c r="Y488" s="9"/>
     </row>
-    <row r="489" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="8">
         <v>149024</v>
       </c>
@@ -40934,8 +41561,12 @@
         <v>57</v>
       </c>
       <c r="Y489" s="9"/>
-    </row>
-    <row r="490" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z489" s="15">
+        <f>_xlfn.XLOOKUP(A489,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>149024</v>
+      </c>
+    </row>
+    <row r="490" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="16">
         <v>146029</v>
       </c>
@@ -41000,7 +41631,7 @@
       </c>
       <c r="Y490" s="9"/>
     </row>
-    <row r="491" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="16">
         <v>233027</v>
       </c>
@@ -41063,7 +41694,7 @@
       </c>
       <c r="Y491" s="9"/>
     </row>
-    <row r="492" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="16">
         <v>257037</v>
       </c>
@@ -41124,7 +41755,7 @@
       </c>
       <c r="Y492" s="9"/>
     </row>
-    <row r="493" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="8">
         <v>257039</v>
       </c>
@@ -41190,8 +41821,12 @@
         <v>57</v>
       </c>
       <c r="Y493" s="9"/>
-    </row>
-    <row r="494" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z493" s="15">
+        <f>_xlfn.XLOOKUP(A493,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>257039</v>
+      </c>
+    </row>
+    <row r="494" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="16">
         <v>260050</v>
       </c>
@@ -41254,7 +41889,7 @@
       </c>
       <c r="Y494" s="9"/>
     </row>
-    <row r="495" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="16">
         <v>266035</v>
       </c>
@@ -41317,7 +41952,7 @@
       </c>
       <c r="Y495" s="9"/>
     </row>
-    <row r="496" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="16">
         <v>267032</v>
       </c>
@@ -41378,7 +42013,7 @@
       </c>
       <c r="Y496" s="9"/>
     </row>
-    <row r="497" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="16">
         <v>269010</v>
       </c>
@@ -41439,7 +42074,7 @@
       </c>
       <c r="Y497" s="9"/>
     </row>
-    <row r="498" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="16">
         <v>233060</v>
       </c>
@@ -41496,7 +42131,7 @@
       </c>
       <c r="Y498" s="9"/>
     </row>
-    <row r="499" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="8">
         <v>244023</v>
       </c>
@@ -41562,8 +42197,12 @@
         <v>57</v>
       </c>
       <c r="Y499" s="9"/>
-    </row>
-    <row r="500" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z499" s="15">
+        <f>_xlfn.XLOOKUP(A499,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>244023</v>
+      </c>
+    </row>
+    <row r="500" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="16">
         <v>256001</v>
       </c>
@@ -41622,7 +42261,7 @@
       </c>
       <c r="Y500" s="9"/>
     </row>
-    <row r="501" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="16">
         <v>266004</v>
       </c>
@@ -41685,7 +42324,7 @@
       </c>
       <c r="Y501" s="9"/>
     </row>
-    <row r="502" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="16">
         <v>266082</v>
       </c>
@@ -41748,7 +42387,7 @@
       </c>
       <c r="Y502" s="9"/>
     </row>
-    <row r="503" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:26" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="8">
         <v>166006</v>
       </c>
@@ -41810,8 +42449,12 @@
       <c r="Y503" s="9" t="s">
         <v>2979</v>
       </c>
-    </row>
-    <row r="504" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z503" s="15" t="e">
+        <f>_xlfn.XLOOKUP(A503,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="504" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="16">
         <v>169012</v>
       </c>
@@ -41868,7 +42511,7 @@
       </c>
       <c r="Y504" s="9"/>
     </row>
-    <row r="505" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="8">
         <v>241009</v>
       </c>
@@ -41928,8 +42571,12 @@
         <v>57</v>
       </c>
       <c r="Y505" s="9"/>
-    </row>
-    <row r="506" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z505" s="15">
+        <f>_xlfn.XLOOKUP(A505,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>241009</v>
+      </c>
+    </row>
+    <row r="506" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="16">
         <v>147029</v>
       </c>
@@ -41988,7 +42635,7 @@
       </c>
       <c r="Y506" s="9"/>
     </row>
-    <row r="507" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="16">
         <v>149039</v>
       </c>
@@ -42049,7 +42696,7 @@
       </c>
       <c r="Y507" s="9"/>
     </row>
-    <row r="508" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="16">
         <v>151015</v>
       </c>
@@ -42114,7 +42761,7 @@
       </c>
       <c r="Y508" s="9"/>
     </row>
-    <row r="509" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="16">
         <v>160004</v>
       </c>
@@ -42175,7 +42822,7 @@
       </c>
       <c r="Y509" s="9"/>
     </row>
-    <row r="510" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="16">
         <v>161010</v>
       </c>
@@ -42236,7 +42883,7 @@
       </c>
       <c r="Y510" s="9"/>
     </row>
-    <row r="511" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="16">
         <v>166026</v>
       </c>
@@ -42295,7 +42942,7 @@
       </c>
       <c r="Y511" s="9"/>
     </row>
-    <row r="512" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="16">
         <v>166034</v>
       </c>
@@ -42352,7 +42999,7 @@
       </c>
       <c r="Y512" s="9"/>
     </row>
-    <row r="513" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="16">
         <v>167009</v>
       </c>
@@ -42409,7 +43056,7 @@
       </c>
       <c r="Y513" s="9"/>
     </row>
-    <row r="514" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="16">
         <v>136028</v>
       </c>
@@ -42468,7 +43115,7 @@
       </c>
       <c r="Y514" s="9"/>
     </row>
-    <row r="515" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="16">
         <v>150029</v>
       </c>
@@ -42529,7 +43176,7 @@
       </c>
       <c r="Y515" s="9"/>
     </row>
-    <row r="516" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="16">
         <v>245017</v>
       </c>
@@ -42594,7 +43241,7 @@
       </c>
       <c r="Y516" s="9"/>
     </row>
-    <row r="517" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="8">
         <v>368001</v>
       </c>
@@ -42656,8 +43303,12 @@
         <v>33</v>
       </c>
       <c r="Y517" s="9"/>
-    </row>
-    <row r="518" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z517" s="15">
+        <f>_xlfn.XLOOKUP(A517,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>368001</v>
+      </c>
+    </row>
+    <row r="518" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="8">
         <v>148005</v>
       </c>
@@ -42723,8 +43374,12 @@
         <v>57</v>
       </c>
       <c r="Y518" s="9"/>
-    </row>
-    <row r="519" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z518" s="15">
+        <f>_xlfn.XLOOKUP(A518,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>148005</v>
+      </c>
+    </row>
+    <row r="519" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="16">
         <v>168003</v>
       </c>
@@ -42785,7 +43440,7 @@
       </c>
       <c r="Y519" s="9"/>
     </row>
-    <row r="520" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="16">
         <v>169014</v>
       </c>
@@ -42846,7 +43501,7 @@
       </c>
       <c r="Y520" s="9"/>
     </row>
-    <row r="521" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="16">
         <v>158053</v>
       </c>
@@ -42911,7 +43566,7 @@
       </c>
       <c r="Y521" s="9"/>
     </row>
-    <row r="522" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="16">
         <v>166018</v>
       </c>
@@ -42968,7 +43623,7 @@
       </c>
       <c r="Y522" s="9"/>
     </row>
-    <row r="523" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="16">
         <v>167010</v>
       </c>
@@ -43029,7 +43684,7 @@
       </c>
       <c r="Y523" s="9"/>
     </row>
-    <row r="524" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="16">
         <v>167007</v>
       </c>
@@ -43092,7 +43747,7 @@
       </c>
       <c r="Y524" s="9"/>
     </row>
-    <row r="525" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="16">
         <v>169013</v>
       </c>
@@ -43153,7 +43808,7 @@
       </c>
       <c r="Y525" s="9"/>
     </row>
-    <row r="526" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="16">
         <v>161014</v>
       </c>
@@ -43216,7 +43871,7 @@
       </c>
       <c r="Y526" s="9"/>
     </row>
-    <row r="527" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="16">
         <v>167036</v>
       </c>
@@ -43275,7 +43930,7 @@
       </c>
       <c r="Y527" s="9"/>
     </row>
-    <row r="528" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="8" t="s">
         <v>2701</v>
       </c>
@@ -43337,12 +43992,16 @@
       <c r="Y528" s="9" t="s">
         <v>3146</v>
       </c>
-    </row>
-    <row r="529" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z528" s="15" t="str">
+        <f>_xlfn.XLOOKUP(A528,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>268029 A</v>
+      </c>
+    </row>
+    <row r="529" spans="1:26" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="8">
         <v>169024</v>
       </c>
-      <c r="B529" s="33" t="s">
+      <c r="B529" s="31" t="s">
         <v>3147</v>
       </c>
       <c r="C529" s="9" t="s">
@@ -43400,8 +44059,12 @@
       <c r="Y529" s="9" t="s">
         <v>3154</v>
       </c>
-    </row>
-    <row r="530" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z529" s="15" t="e">
+        <f>_xlfn.XLOOKUP(A529,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="530" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="8">
         <v>656001</v>
       </c>
@@ -43459,8 +44122,12 @@
         <v>3</v>
       </c>
       <c r="Y530" s="9"/>
-    </row>
-    <row r="531" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z530" s="15">
+        <f>_xlfn.XLOOKUP(A530,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>656001</v>
+      </c>
+    </row>
+    <row r="531" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="8">
         <v>656008</v>
       </c>
@@ -43522,8 +44189,12 @@
         <v>33</v>
       </c>
       <c r="Y531" s="9"/>
-    </row>
-    <row r="532" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Z531" s="15">
+        <f>_xlfn.XLOOKUP(A531,[1]กรอกข้อมูล!$A:$A,[1]กรอกข้อมูล!$A:$A)</f>
+        <v>656008</v>
+      </c>
+    </row>
+    <row r="532" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="16">
         <v>269029</v>
       </c>
@@ -43582,7 +44253,7 @@
       </c>
       <c r="Y532" s="9"/>
     </row>
-    <row r="533" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="16">
         <v>169022</v>
       </c>
@@ -43643,7 +44314,7 @@
       </c>
       <c r="Y533" s="9"/>
     </row>
-    <row r="534" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="16">
         <v>269034</v>
       </c>
@@ -43704,7 +44375,7 @@
       </c>
       <c r="Y534" s="9"/>
     </row>
-    <row r="535" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="16">
         <v>269038</v>
       </c>
@@ -43763,7 +44434,7 @@
       </c>
       <c r="Y535" s="9"/>
     </row>
-    <row r="536" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="16">
         <v>269033</v>
       </c>
@@ -43824,7 +44495,7 @@
       </c>
       <c r="Y536" s="9"/>
     </row>
-    <row r="537" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="16">
         <v>269037</v>
       </c>
@@ -43883,7 +44554,7 @@
       </c>
       <c r="Y537" s="9"/>
     </row>
-    <row r="538" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="16">
         <v>269036</v>
       </c>
@@ -43942,7 +44613,7 @@
       </c>
       <c r="Y538" s="9"/>
     </row>
-    <row r="539" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="16">
         <v>269035</v>
       </c>
@@ -44001,7 +44672,7 @@
       </c>
       <c r="Y539" s="9"/>
     </row>
-    <row r="540" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="16">
         <v>269039</v>
       </c>
@@ -44062,7 +44733,7 @@
       </c>
       <c r="Y540" s="9"/>
     </row>
-    <row r="541" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="16">
         <v>269041</v>
       </c>
@@ -44123,7 +44794,7 @@
       </c>
       <c r="Y541" s="9"/>
     </row>
-    <row r="542" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="16">
         <v>269042</v>
       </c>
@@ -44182,7 +44853,7 @@
       </c>
       <c r="Y542" s="9"/>
     </row>
-    <row r="543" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="16">
         <v>169025</v>
       </c>
@@ -44243,7 +44914,7 @@
       </c>
       <c r="Y543" s="9"/>
     </row>
-    <row r="544" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:26" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="16">
         <v>169026</v>
       </c>
@@ -44304,7 +44975,7 @@
       </c>
       <c r="Y544" s="9"/>
     </row>
-    <row r="545" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="16">
         <v>169027</v>
       </c>
@@ -44365,7 +45036,7 @@
       </c>
       <c r="Y545" s="9"/>
     </row>
-    <row r="546" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="16">
         <v>269045</v>
       </c>
@@ -44424,7 +45095,7 @@
       </c>
       <c r="Y546" s="9"/>
     </row>
-    <row r="547" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="16">
         <v>269044</v>
       </c>
@@ -44485,7 +45156,7 @@
       </c>
       <c r="Y547" s="9"/>
     </row>
-    <row r="548" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="16">
         <v>169028</v>
       </c>
@@ -44544,7 +45215,7 @@
       </c>
       <c r="Y548" s="9"/>
     </row>
-    <row r="549" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="16">
         <v>169030</v>
       </c>
@@ -44603,7 +45274,7 @@
       </c>
       <c r="Y549" s="9"/>
     </row>
-    <row r="550" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="16">
         <v>169029</v>
       </c>
@@ -44662,7 +45333,7 @@
       </c>
       <c r="Y550" s="9"/>
     </row>
-    <row r="551" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="16">
         <v>269050</v>
       </c>
@@ -44719,7 +45390,7 @@
       </c>
       <c r="Y551" s="9"/>
     </row>
-    <row r="552" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="16">
         <v>269053</v>
       </c>
@@ -44776,7 +45447,7 @@
       </c>
       <c r="Y552" s="9"/>
     </row>
-    <row r="553" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="16">
         <v>269052</v>
       </c>
@@ -44835,7 +45506,7 @@
       </c>
       <c r="Y553" s="9"/>
     </row>
-    <row r="554" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="16">
         <v>269047</v>
       </c>
@@ -44892,7 +45563,7 @@
       </c>
       <c r="Y554" s="9"/>
     </row>
-    <row r="555" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="16">
         <v>169031</v>
       </c>
@@ -44951,7 +45622,7 @@
       </c>
       <c r="Y555" s="9"/>
     </row>
-    <row r="556" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="16">
         <v>469004</v>
       </c>
@@ -45008,7 +45679,7 @@
       </c>
       <c r="Y556" s="9"/>
     </row>
-    <row r="557" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="16" t="s">
         <v>3485</v>
       </c>
@@ -45059,7 +45730,7 @@
       <c r="X557" s="9"/>
       <c r="Y557" s="9"/>
     </row>
-    <row r="558" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="16">
         <v>269058</v>
       </c>
@@ -45116,7 +45787,7 @@
       </c>
       <c r="Y558" s="9"/>
     </row>
-    <row r="559" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="16">
         <v>269064</v>
       </c>
@@ -45173,7 +45844,7 @@
       </c>
       <c r="Y559" s="9"/>
     </row>
-    <row r="560" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="16">
         <v>169034</v>
       </c>
@@ -45232,7 +45903,7 @@
       </c>
       <c r="Y560" s="9"/>
     </row>
-    <row r="561" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="16">
         <v>169036</v>
       </c>
@@ -45291,7 +45962,7 @@
       </c>
       <c r="Y561" s="9"/>
     </row>
-    <row r="562" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="16">
         <v>269054</v>
       </c>
@@ -45350,7 +46021,7 @@
       </c>
       <c r="Y562" s="9"/>
     </row>
-    <row r="563" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="16">
         <v>269055</v>
       </c>
@@ -45409,7 +46080,7 @@
       </c>
       <c r="Y563" s="9"/>
     </row>
-    <row r="564" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="16">
         <v>269056</v>
       </c>
@@ -45468,7 +46139,7 @@
       </c>
       <c r="Y564" s="9"/>
     </row>
-    <row r="565" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="16">
         <v>269057</v>
       </c>
@@ -45527,7 +46198,7 @@
       </c>
       <c r="Y565" s="9"/>
     </row>
-    <row r="566" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="16">
         <v>269063</v>
       </c>
@@ -45584,7 +46255,7 @@
       </c>
       <c r="Y566" s="9"/>
     </row>
-    <row r="567" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="16">
         <v>269061</v>
       </c>
@@ -45641,7 +46312,7 @@
       </c>
       <c r="Y567" s="9"/>
     </row>
-    <row r="568" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="16">
         <v>269065</v>
       </c>
@@ -45700,7 +46371,7 @@
       </c>
       <c r="Y568" s="9"/>
     </row>
-    <row r="569" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="16">
         <v>169035</v>
       </c>
@@ -47476,7 +48147,18 @@
       <c r="B1000"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AE569" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AE569" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="16">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="25">
+      <filters>
+        <filter val="#N/A"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:X1"/>
   </mergeCells>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="14_{85CD52BF-2C13-4EA1-A181-6633CD8D816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CD1657A-2BDD-47E9-992E-527232E48067}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="14_{85CD52BF-2C13-4EA1-A181-6633CD8D816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4E0C46F-DAF0-403F-9574-76A9D74FD5F5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8172" uniqueCount="3504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8171" uniqueCount="3504">
   <si>
     <t>emp_id</t>
   </si>
@@ -43275,7 +43275,7 @@
       </c>
       <c r="Y527" s="9"/>
     </row>
-    <row r="528" spans="1:25" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:25" s="15" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="8" t="s">
         <v>2701</v>
       </c>
@@ -43318,9 +43318,7 @@
         <v>1202</v>
       </c>
       <c r="P528" s="9"/>
-      <c r="Q528" s="13" t="s">
-        <v>32</v>
-      </c>
+      <c r="Q528" s="9"/>
       <c r="R528" s="9"/>
       <c r="S528" s="9"/>
       <c r="T528" s="9"/>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="14_{85CD52BF-2C13-4EA1-A181-6633CD8D816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{905C172A-992F-44D3-82EB-F7739869C9F8}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="14_{85CD52BF-2C13-4EA1-A181-6633CD8D816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5415DC89-BFF9-4B84-8A8B-AF570D6926EB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8170" uniqueCount="3503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8171" uniqueCount="3503">
   <si>
     <t>emp_id</t>
   </si>
@@ -10804,17 +10804,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -21510,7 +21500,9 @@
       <c r="T167" s="9" t="s">
         <v>1194</v>
       </c>
-      <c r="U167" s="14"/>
+      <c r="U167" s="14" t="s">
+        <v>2885</v>
+      </c>
       <c r="V167" s="9">
         <v>3</v>
       </c>
@@ -40943,7 +40935,7 @@
         <v>3502</v>
       </c>
       <c r="G489" s="9" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H489" s="13" t="s">
         <v>2883</v>
@@ -47534,29 +47526,29 @@
     <mergeCell ref="A1:X1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I166">
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I466">
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I561">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I562">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I563">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I564">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I565">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="O166" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -50021,7 +50013,7 @@
   </sheetData>
   <autoFilter ref="A1:F122" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
